--- a/backend/templates/D155A/W41_Add_Service.xlsx
+++ b/backend/templates/D155A/W41_Add_Service.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Motasem.ghanem\EQP-System\backend\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Motasem.ghanem\EQP-System\backend\templates\D155A\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1444,6 +1444,280 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -1460,18 +1734,20 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1496,282 +1772,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2275,7 +2275,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" s="2" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="260" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
@@ -2289,60 +2289,60 @@
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
       <c r="AM1" s="1"/>
-      <c r="AN1" s="179" t="s">
+      <c r="AN1" s="261" t="s">
         <v>151</v>
       </c>
-      <c r="AO1" s="179"/>
-      <c r="AP1" s="179"/>
-      <c r="AQ1" s="179"/>
-      <c r="AR1" s="179"/>
-      <c r="AS1" s="179"/>
-      <c r="AT1" s="179"/>
-      <c r="AU1" s="179"/>
-      <c r="AV1" s="179"/>
-      <c r="AW1" s="179"/>
-      <c r="AX1" s="179"/>
-      <c r="AY1" s="179"/>
-      <c r="AZ1" s="179"/>
-      <c r="BA1" s="179"/>
-      <c r="BB1" s="179"/>
-      <c r="BC1" s="179"/>
-      <c r="BD1" s="179"/>
-      <c r="BE1" s="179"/>
-      <c r="BF1" s="179"/>
-      <c r="BG1" s="179"/>
-      <c r="BH1" s="179"/>
+      <c r="AO1" s="261"/>
+      <c r="AP1" s="261"/>
+      <c r="AQ1" s="261"/>
+      <c r="AR1" s="261"/>
+      <c r="AS1" s="261"/>
+      <c r="AT1" s="261"/>
+      <c r="AU1" s="261"/>
+      <c r="AV1" s="261"/>
+      <c r="AW1" s="261"/>
+      <c r="AX1" s="261"/>
+      <c r="AY1" s="261"/>
+      <c r="AZ1" s="261"/>
+      <c r="BA1" s="261"/>
+      <c r="BB1" s="261"/>
+      <c r="BC1" s="261"/>
+      <c r="BD1" s="261"/>
+      <c r="BE1" s="261"/>
+      <c r="BF1" s="261"/>
+      <c r="BG1" s="261"/>
+      <c r="BH1" s="261"/>
     </row>
     <row r="2" spans="1:60" ht="3" customHeight="1">
-      <c r="A2" s="178"/>
+      <c r="A2" s="260"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="V2" s="180" t="s">
+      <c r="V2" s="262" t="s">
         <v>1</v>
       </c>
-      <c r="W2" s="180"/>
-      <c r="X2" s="180"/>
-      <c r="Y2" s="180"/>
-      <c r="Z2" s="180"/>
-      <c r="AA2" s="180"/>
-      <c r="AB2" s="180"/>
-      <c r="AC2" s="180"/>
-      <c r="AD2" s="180"/>
-      <c r="AE2" s="180"/>
-      <c r="AF2" s="180"/>
-      <c r="AG2" s="180"/>
-      <c r="AH2" s="180"/>
-      <c r="AI2" s="180"/>
-      <c r="AJ2" s="180"/>
-      <c r="AK2" s="180"/>
-      <c r="AL2" s="180"/>
+      <c r="W2" s="262"/>
+      <c r="X2" s="262"/>
+      <c r="Y2" s="262"/>
+      <c r="Z2" s="262"/>
+      <c r="AA2" s="262"/>
+      <c r="AB2" s="262"/>
+      <c r="AC2" s="262"/>
+      <c r="AD2" s="262"/>
+      <c r="AE2" s="262"/>
+      <c r="AF2" s="262"/>
+      <c r="AG2" s="262"/>
+      <c r="AH2" s="262"/>
+      <c r="AI2" s="262"/>
+      <c r="AJ2" s="262"/>
+      <c r="AK2" s="262"/>
+      <c r="AL2" s="262"/>
       <c r="AM2" s="3"/>
     </row>
     <row r="3" spans="1:60" ht="9.75" customHeight="1">
-      <c r="A3" s="178"/>
+      <c r="A3" s="260"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -2363,50 +2363,50 @@
       <c r="S3" s="5"/>
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
-      <c r="V3" s="180"/>
-      <c r="W3" s="180"/>
-      <c r="X3" s="180"/>
-      <c r="Y3" s="180"/>
-      <c r="Z3" s="180"/>
-      <c r="AA3" s="180"/>
-      <c r="AB3" s="180"/>
-      <c r="AC3" s="180"/>
-      <c r="AD3" s="180"/>
-      <c r="AE3" s="180"/>
-      <c r="AF3" s="180"/>
-      <c r="AG3" s="180"/>
-      <c r="AH3" s="180"/>
-      <c r="AI3" s="180"/>
-      <c r="AJ3" s="180"/>
-      <c r="AK3" s="180"/>
-      <c r="AL3" s="180"/>
+      <c r="V3" s="262"/>
+      <c r="W3" s="262"/>
+      <c r="X3" s="262"/>
+      <c r="Y3" s="262"/>
+      <c r="Z3" s="262"/>
+      <c r="AA3" s="262"/>
+      <c r="AB3" s="262"/>
+      <c r="AC3" s="262"/>
+      <c r="AD3" s="262"/>
+      <c r="AE3" s="262"/>
+      <c r="AF3" s="262"/>
+      <c r="AG3" s="262"/>
+      <c r="AH3" s="262"/>
+      <c r="AI3" s="262"/>
+      <c r="AJ3" s="262"/>
+      <c r="AK3" s="262"/>
+      <c r="AL3" s="262"/>
       <c r="AM3" s="6"/>
       <c r="AN3" s="7"/>
       <c r="AO3" s="8"/>
-      <c r="AP3" s="181" t="s">
+      <c r="AP3" s="263" t="s">
         <v>2</v>
       </c>
-      <c r="AQ3" s="181"/>
-      <c r="AR3" s="181"/>
-      <c r="AS3" s="181"/>
-      <c r="AT3" s="181"/>
-      <c r="AU3" s="181"/>
-      <c r="AV3" s="181"/>
-      <c r="AW3" s="181"/>
-      <c r="AX3" s="181"/>
-      <c r="AY3" s="181"/>
-      <c r="AZ3" s="181"/>
-      <c r="BA3" s="181"/>
-      <c r="BB3" s="181"/>
-      <c r="BC3" s="181"/>
-      <c r="BD3" s="181"/>
-      <c r="BE3" s="181"/>
+      <c r="AQ3" s="263"/>
+      <c r="AR3" s="263"/>
+      <c r="AS3" s="263"/>
+      <c r="AT3" s="263"/>
+      <c r="AU3" s="263"/>
+      <c r="AV3" s="263"/>
+      <c r="AW3" s="263"/>
+      <c r="AX3" s="263"/>
+      <c r="AY3" s="263"/>
+      <c r="AZ3" s="263"/>
+      <c r="BA3" s="263"/>
+      <c r="BB3" s="263"/>
+      <c r="BC3" s="263"/>
+      <c r="BD3" s="263"/>
+      <c r="BE3" s="263"/>
       <c r="BF3" s="9"/>
       <c r="BG3" s="9"/>
       <c r="BH3" s="9"/>
     </row>
     <row r="4" spans="1:60" ht="15" customHeight="1">
-      <c r="A4" s="178"/>
+      <c r="A4" s="260"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -2427,70 +2427,70 @@
       <c r="S4" s="5"/>
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
-      <c r="V4" s="180"/>
-      <c r="W4" s="180"/>
-      <c r="X4" s="180"/>
-      <c r="Y4" s="180"/>
-      <c r="Z4" s="180"/>
-      <c r="AA4" s="180"/>
-      <c r="AB4" s="180"/>
-      <c r="AC4" s="180"/>
-      <c r="AD4" s="180"/>
-      <c r="AE4" s="180"/>
-      <c r="AF4" s="180"/>
-      <c r="AG4" s="180"/>
-      <c r="AH4" s="180"/>
-      <c r="AI4" s="180"/>
-      <c r="AJ4" s="180"/>
-      <c r="AK4" s="180"/>
-      <c r="AL4" s="180"/>
+      <c r="V4" s="262"/>
+      <c r="W4" s="262"/>
+      <c r="X4" s="262"/>
+      <c r="Y4" s="262"/>
+      <c r="Z4" s="262"/>
+      <c r="AA4" s="262"/>
+      <c r="AB4" s="262"/>
+      <c r="AC4" s="262"/>
+      <c r="AD4" s="262"/>
+      <c r="AE4" s="262"/>
+      <c r="AF4" s="262"/>
+      <c r="AG4" s="262"/>
+      <c r="AH4" s="262"/>
+      <c r="AI4" s="262"/>
+      <c r="AJ4" s="262"/>
+      <c r="AK4" s="262"/>
+      <c r="AL4" s="262"/>
       <c r="AM4" s="10"/>
       <c r="AN4" s="11"/>
       <c r="AO4" s="12"/>
-      <c r="AP4" s="182"/>
-      <c r="AQ4" s="182"/>
-      <c r="AR4" s="182"/>
-      <c r="AS4" s="182"/>
-      <c r="AT4" s="182"/>
-      <c r="AU4" s="182"/>
-      <c r="AV4" s="182"/>
-      <c r="AW4" s="182"/>
-      <c r="AX4" s="182"/>
-      <c r="AY4" s="182"/>
-      <c r="AZ4" s="182"/>
-      <c r="BA4" s="182"/>
-      <c r="BB4" s="182"/>
-      <c r="BC4" s="182"/>
-      <c r="BD4" s="182"/>
-      <c r="BE4" s="182"/>
+      <c r="AP4" s="264"/>
+      <c r="AQ4" s="264"/>
+      <c r="AR4" s="264"/>
+      <c r="AS4" s="264"/>
+      <c r="AT4" s="264"/>
+      <c r="AU4" s="264"/>
+      <c r="AV4" s="264"/>
+      <c r="AW4" s="264"/>
+      <c r="AX4" s="264"/>
+      <c r="AY4" s="264"/>
+      <c r="AZ4" s="264"/>
+      <c r="BA4" s="264"/>
+      <c r="BB4" s="264"/>
+      <c r="BC4" s="264"/>
+      <c r="BD4" s="264"/>
+      <c r="BE4" s="264"/>
       <c r="BF4" s="9"/>
       <c r="BG4" s="9"/>
       <c r="BH4" s="9"/>
     </row>
     <row r="5" spans="1:60" ht="3" customHeight="1">
-      <c r="A5" s="178"/>
+      <c r="A5" s="260"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="V5" s="180"/>
-      <c r="W5" s="180"/>
-      <c r="X5" s="180"/>
-      <c r="Y5" s="180"/>
-      <c r="Z5" s="180"/>
-      <c r="AA5" s="180"/>
-      <c r="AB5" s="180"/>
-      <c r="AC5" s="180"/>
-      <c r="AD5" s="180"/>
-      <c r="AE5" s="180"/>
-      <c r="AF5" s="180"/>
-      <c r="AG5" s="180"/>
-      <c r="AH5" s="180"/>
-      <c r="AI5" s="180"/>
-      <c r="AJ5" s="180"/>
-      <c r="AK5" s="180"/>
-      <c r="AL5" s="180"/>
+      <c r="V5" s="262"/>
+      <c r="W5" s="262"/>
+      <c r="X5" s="262"/>
+      <c r="Y5" s="262"/>
+      <c r="Z5" s="262"/>
+      <c r="AA5" s="262"/>
+      <c r="AB5" s="262"/>
+      <c r="AC5" s="262"/>
+      <c r="AD5" s="262"/>
+      <c r="AE5" s="262"/>
+      <c r="AF5" s="262"/>
+      <c r="AG5" s="262"/>
+      <c r="AH5" s="262"/>
+      <c r="AI5" s="262"/>
+      <c r="AJ5" s="262"/>
+      <c r="AK5" s="262"/>
+      <c r="AL5" s="262"/>
       <c r="AM5" s="13"/>
       <c r="AN5" s="9"/>
       <c r="AO5" s="9"/>
@@ -2515,7 +2515,7 @@
       <c r="BH5" s="9"/>
     </row>
     <row r="6" spans="1:60" ht="14.25" customHeight="1">
-      <c r="A6" s="178"/>
+      <c r="A6" s="260"/>
       <c r="B6" s="14"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -2553,328 +2553,328 @@
       <c r="AK6" s="3"/>
       <c r="AL6" s="3"/>
       <c r="AM6" s="3"/>
-      <c r="AN6" s="183" t="s">
+      <c r="AN6" s="258" t="s">
         <v>3</v>
       </c>
-      <c r="AO6" s="183"/>
-      <c r="AP6" s="183"/>
-      <c r="AQ6" s="184"/>
-      <c r="AR6" s="272" t="s">
+      <c r="AO6" s="258"/>
+      <c r="AP6" s="258"/>
+      <c r="AQ6" s="265"/>
+      <c r="AR6" s="266" t="s">
         <v>4</v>
       </c>
-      <c r="AS6" s="272"/>
-      <c r="AT6" s="272" t="s">
+      <c r="AS6" s="266"/>
+      <c r="AT6" s="266" t="s">
         <v>5</v>
       </c>
-      <c r="AU6" s="272"/>
-      <c r="AV6" s="272" t="s">
+      <c r="AU6" s="266"/>
+      <c r="AV6" s="266" t="s">
         <v>6</v>
       </c>
-      <c r="AW6" s="272"/>
-      <c r="AX6" s="272" t="s">
+      <c r="AW6" s="266"/>
+      <c r="AX6" s="266" t="s">
         <v>7</v>
       </c>
-      <c r="AY6" s="272"/>
-      <c r="AZ6" s="272" t="s">
+      <c r="AY6" s="266"/>
+      <c r="AZ6" s="266" t="s">
         <v>8</v>
       </c>
-      <c r="BA6" s="272"/>
-      <c r="BB6" s="272" t="s">
+      <c r="BA6" s="266"/>
+      <c r="BB6" s="266" t="s">
         <v>9</v>
       </c>
-      <c r="BC6" s="272"/>
-      <c r="BD6" s="272" t="s">
+      <c r="BC6" s="266"/>
+      <c r="BD6" s="266" t="s">
         <v>10</v>
       </c>
-      <c r="BE6" s="272"/>
+      <c r="BE6" s="266"/>
       <c r="BF6" s="13"/>
       <c r="BG6" s="9"/>
       <c r="BH6" s="9"/>
     </row>
     <row r="7" spans="1:60" ht="11.1" customHeight="1">
-      <c r="A7" s="178"/>
-      <c r="B7" s="193" t="s">
+      <c r="A7" s="260"/>
+      <c r="B7" s="236" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="193"/>
-      <c r="D7" s="193"/>
-      <c r="E7" s="193"/>
-      <c r="F7" s="193"/>
-      <c r="G7" s="193"/>
-      <c r="H7" s="193"/>
-      <c r="I7" s="194" t="s">
+      <c r="C7" s="236"/>
+      <c r="D7" s="236"/>
+      <c r="E7" s="236"/>
+      <c r="F7" s="236"/>
+      <c r="G7" s="236"/>
+      <c r="H7" s="236"/>
+      <c r="I7" s="242" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="194"/>
-      <c r="K7" s="194"/>
-      <c r="L7" s="195" t="s">
+      <c r="J7" s="242"/>
+      <c r="K7" s="242"/>
+      <c r="L7" s="243" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="196"/>
-      <c r="N7" s="196"/>
-      <c r="O7" s="196"/>
-      <c r="P7" s="196"/>
-      <c r="Q7" s="196"/>
-      <c r="R7" s="196"/>
-      <c r="S7" s="196"/>
-      <c r="T7" s="197"/>
+      <c r="M7" s="244"/>
+      <c r="N7" s="244"/>
+      <c r="O7" s="244"/>
+      <c r="P7" s="244"/>
+      <c r="Q7" s="244"/>
+      <c r="R7" s="244"/>
+      <c r="S7" s="244"/>
+      <c r="T7" s="245"/>
       <c r="U7" s="13"/>
-      <c r="V7" s="193" t="s">
+      <c r="V7" s="236" t="s">
         <v>14</v>
       </c>
-      <c r="W7" s="193"/>
-      <c r="X7" s="193"/>
-      <c r="Y7" s="193"/>
-      <c r="Z7" s="193"/>
-      <c r="AA7" s="193"/>
-      <c r="AB7" s="193"/>
-      <c r="AC7" s="193"/>
-      <c r="AD7" s="201" t="s">
+      <c r="W7" s="236"/>
+      <c r="X7" s="236"/>
+      <c r="Y7" s="236"/>
+      <c r="Z7" s="236"/>
+      <c r="AA7" s="236"/>
+      <c r="AB7" s="236"/>
+      <c r="AC7" s="236"/>
+      <c r="AD7" s="249" t="s">
         <v>13</v>
       </c>
-      <c r="AE7" s="201"/>
-      <c r="AF7" s="201"/>
-      <c r="AG7" s="201"/>
-      <c r="AH7" s="201"/>
-      <c r="AI7" s="201"/>
-      <c r="AJ7" s="201"/>
-      <c r="AK7" s="201"/>
-      <c r="AL7" s="201"/>
+      <c r="AE7" s="249"/>
+      <c r="AF7" s="249"/>
+      <c r="AG7" s="249"/>
+      <c r="AH7" s="249"/>
+      <c r="AI7" s="249"/>
+      <c r="AJ7" s="249"/>
+      <c r="AK7" s="249"/>
+      <c r="AL7" s="249"/>
       <c r="AM7" s="3"/>
-      <c r="AN7" s="183"/>
-      <c r="AO7" s="183"/>
-      <c r="AP7" s="183"/>
-      <c r="AQ7" s="184"/>
-      <c r="AR7" s="272"/>
-      <c r="AS7" s="272"/>
-      <c r="AT7" s="272"/>
-      <c r="AU7" s="272"/>
-      <c r="AV7" s="272"/>
-      <c r="AW7" s="272"/>
-      <c r="AX7" s="272"/>
-      <c r="AY7" s="272"/>
-      <c r="AZ7" s="272"/>
-      <c r="BA7" s="272"/>
-      <c r="BB7" s="272"/>
-      <c r="BC7" s="272"/>
-      <c r="BD7" s="272"/>
-      <c r="BE7" s="272"/>
+      <c r="AN7" s="258"/>
+      <c r="AO7" s="258"/>
+      <c r="AP7" s="258"/>
+      <c r="AQ7" s="265"/>
+      <c r="AR7" s="266"/>
+      <c r="AS7" s="266"/>
+      <c r="AT7" s="266"/>
+      <c r="AU7" s="266"/>
+      <c r="AV7" s="266"/>
+      <c r="AW7" s="266"/>
+      <c r="AX7" s="266"/>
+      <c r="AY7" s="266"/>
+      <c r="AZ7" s="266"/>
+      <c r="BA7" s="266"/>
+      <c r="BB7" s="266"/>
+      <c r="BC7" s="266"/>
+      <c r="BD7" s="266"/>
+      <c r="BE7" s="266"/>
       <c r="BF7" s="13"/>
-      <c r="BG7" s="185"/>
-      <c r="BH7" s="185"/>
+      <c r="BG7" s="267"/>
+      <c r="BH7" s="267"/>
     </row>
     <row r="8" spans="1:60" ht="11.1" customHeight="1">
-      <c r="A8" s="178"/>
-      <c r="B8" s="193"/>
-      <c r="C8" s="193"/>
-      <c r="D8" s="193"/>
-      <c r="E8" s="193"/>
-      <c r="F8" s="193"/>
-      <c r="G8" s="193"/>
-      <c r="H8" s="193"/>
-      <c r="I8" s="194"/>
-      <c r="J8" s="194"/>
-      <c r="K8" s="194"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="199"/>
-      <c r="N8" s="199"/>
-      <c r="O8" s="199"/>
-      <c r="P8" s="199"/>
-      <c r="Q8" s="199"/>
-      <c r="R8" s="199"/>
-      <c r="S8" s="199"/>
-      <c r="T8" s="200"/>
+      <c r="A8" s="260"/>
+      <c r="B8" s="236"/>
+      <c r="C8" s="236"/>
+      <c r="D8" s="236"/>
+      <c r="E8" s="236"/>
+      <c r="F8" s="236"/>
+      <c r="G8" s="236"/>
+      <c r="H8" s="236"/>
+      <c r="I8" s="242"/>
+      <c r="J8" s="242"/>
+      <c r="K8" s="242"/>
+      <c r="L8" s="246"/>
+      <c r="M8" s="247"/>
+      <c r="N8" s="247"/>
+      <c r="O8" s="247"/>
+      <c r="P8" s="247"/>
+      <c r="Q8" s="247"/>
+      <c r="R8" s="247"/>
+      <c r="S8" s="247"/>
+      <c r="T8" s="248"/>
       <c r="U8" s="16"/>
-      <c r="V8" s="193"/>
-      <c r="W8" s="193"/>
-      <c r="X8" s="193"/>
-      <c r="Y8" s="193"/>
-      <c r="Z8" s="193"/>
-      <c r="AA8" s="193"/>
-      <c r="AB8" s="193"/>
-      <c r="AC8" s="193"/>
-      <c r="AD8" s="201"/>
-      <c r="AE8" s="201"/>
-      <c r="AF8" s="201"/>
-      <c r="AG8" s="201"/>
-      <c r="AH8" s="201"/>
-      <c r="AI8" s="201"/>
-      <c r="AJ8" s="201"/>
-      <c r="AK8" s="201"/>
-      <c r="AL8" s="201"/>
+      <c r="V8" s="236"/>
+      <c r="W8" s="236"/>
+      <c r="X8" s="236"/>
+      <c r="Y8" s="236"/>
+      <c r="Z8" s="236"/>
+      <c r="AA8" s="236"/>
+      <c r="AB8" s="236"/>
+      <c r="AC8" s="236"/>
+      <c r="AD8" s="249"/>
+      <c r="AE8" s="249"/>
+      <c r="AF8" s="249"/>
+      <c r="AG8" s="249"/>
+      <c r="AH8" s="249"/>
+      <c r="AI8" s="249"/>
+      <c r="AJ8" s="249"/>
+      <c r="AK8" s="249"/>
+      <c r="AL8" s="249"/>
       <c r="AM8" s="3"/>
-      <c r="AN8" s="274" t="s">
+      <c r="AN8" s="268" t="s">
         <v>15</v>
       </c>
-      <c r="AO8" s="274"/>
-      <c r="AP8" s="274"/>
-      <c r="AQ8" s="275"/>
-      <c r="AR8" s="272"/>
-      <c r="AS8" s="272"/>
-      <c r="AT8" s="272"/>
-      <c r="AU8" s="272"/>
-      <c r="AV8" s="272"/>
-      <c r="AW8" s="272"/>
-      <c r="AX8" s="272"/>
-      <c r="AY8" s="272"/>
-      <c r="AZ8" s="272"/>
-      <c r="BA8" s="272"/>
-      <c r="BB8" s="272"/>
-      <c r="BC8" s="272"/>
-      <c r="BD8" s="272"/>
-      <c r="BE8" s="272"/>
+      <c r="AO8" s="268"/>
+      <c r="AP8" s="268"/>
+      <c r="AQ8" s="269"/>
+      <c r="AR8" s="266"/>
+      <c r="AS8" s="266"/>
+      <c r="AT8" s="266"/>
+      <c r="AU8" s="266"/>
+      <c r="AV8" s="266"/>
+      <c r="AW8" s="266"/>
+      <c r="AX8" s="266"/>
+      <c r="AY8" s="266"/>
+      <c r="AZ8" s="266"/>
+      <c r="BA8" s="266"/>
+      <c r="BB8" s="266"/>
+      <c r="BC8" s="266"/>
+      <c r="BD8" s="266"/>
+      <c r="BE8" s="266"/>
       <c r="BF8" s="13"/>
-      <c r="BG8" s="185"/>
-      <c r="BH8" s="185"/>
+      <c r="BG8" s="267"/>
+      <c r="BH8" s="267"/>
     </row>
     <row r="9" spans="1:60" ht="9.9" customHeight="1">
-      <c r="A9" s="178"/>
-      <c r="B9" s="186" t="s">
+      <c r="A9" s="260"/>
+      <c r="B9" s="253" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="186"/>
-      <c r="D9" s="186"/>
-      <c r="E9" s="186"/>
-      <c r="F9" s="186"/>
-      <c r="G9" s="186"/>
-      <c r="H9" s="186"/>
-      <c r="I9" s="186">
+      <c r="C9" s="253"/>
+      <c r="D9" s="253"/>
+      <c r="E9" s="253"/>
+      <c r="F9" s="253"/>
+      <c r="G9" s="253"/>
+      <c r="H9" s="253"/>
+      <c r="I9" s="253">
         <v>6</v>
       </c>
-      <c r="J9" s="186"/>
-      <c r="K9" s="186"/>
-      <c r="L9" s="187"/>
-      <c r="M9" s="188"/>
-      <c r="N9" s="188"/>
-      <c r="O9" s="188"/>
-      <c r="P9" s="188"/>
-      <c r="Q9" s="188"/>
-      <c r="R9" s="188"/>
-      <c r="S9" s="188"/>
-      <c r="T9" s="189"/>
+      <c r="J9" s="253"/>
+      <c r="K9" s="253"/>
+      <c r="L9" s="270"/>
+      <c r="M9" s="271"/>
+      <c r="N9" s="271"/>
+      <c r="O9" s="271"/>
+      <c r="P9" s="271"/>
+      <c r="Q9" s="271"/>
+      <c r="R9" s="271"/>
+      <c r="S9" s="271"/>
+      <c r="T9" s="272"/>
       <c r="U9" s="16"/>
-      <c r="V9" s="187" t="s">
+      <c r="V9" s="270" t="s">
         <v>17</v>
       </c>
-      <c r="W9" s="188"/>
-      <c r="X9" s="188"/>
-      <c r="Y9" s="188"/>
-      <c r="Z9" s="188"/>
-      <c r="AA9" s="188"/>
-      <c r="AB9" s="188"/>
-      <c r="AC9" s="189"/>
-      <c r="AD9" s="186"/>
-      <c r="AE9" s="186"/>
-      <c r="AF9" s="186"/>
-      <c r="AG9" s="186"/>
-      <c r="AH9" s="186"/>
-      <c r="AI9" s="186"/>
-      <c r="AJ9" s="186"/>
-      <c r="AK9" s="186"/>
-      <c r="AL9" s="186"/>
+      <c r="W9" s="271"/>
+      <c r="X9" s="271"/>
+      <c r="Y9" s="271"/>
+      <c r="Z9" s="271"/>
+      <c r="AA9" s="271"/>
+      <c r="AB9" s="271"/>
+      <c r="AC9" s="272"/>
+      <c r="AD9" s="253"/>
+      <c r="AE9" s="253"/>
+      <c r="AF9" s="253"/>
+      <c r="AG9" s="253"/>
+      <c r="AH9" s="253"/>
+      <c r="AI9" s="253"/>
+      <c r="AJ9" s="253"/>
+      <c r="AK9" s="253"/>
+      <c r="AL9" s="253"/>
       <c r="AM9" s="3"/>
-      <c r="AN9" s="274"/>
-      <c r="AO9" s="274"/>
-      <c r="AP9" s="274"/>
-      <c r="AQ9" s="275"/>
-      <c r="AR9" s="272"/>
-      <c r="AS9" s="272"/>
-      <c r="AT9" s="272"/>
-      <c r="AU9" s="272"/>
-      <c r="AV9" s="272"/>
-      <c r="AW9" s="272"/>
-      <c r="AX9" s="272"/>
-      <c r="AY9" s="272"/>
-      <c r="AZ9" s="272"/>
-      <c r="BA9" s="272"/>
-      <c r="BB9" s="272"/>
-      <c r="BC9" s="272"/>
-      <c r="BD9" s="272"/>
-      <c r="BE9" s="272"/>
+      <c r="AN9" s="268"/>
+      <c r="AO9" s="268"/>
+      <c r="AP9" s="268"/>
+      <c r="AQ9" s="269"/>
+      <c r="AR9" s="266"/>
+      <c r="AS9" s="266"/>
+      <c r="AT9" s="266"/>
+      <c r="AU9" s="266"/>
+      <c r="AV9" s="266"/>
+      <c r="AW9" s="266"/>
+      <c r="AX9" s="266"/>
+      <c r="AY9" s="266"/>
+      <c r="AZ9" s="266"/>
+      <c r="BA9" s="266"/>
+      <c r="BB9" s="266"/>
+      <c r="BC9" s="266"/>
+      <c r="BD9" s="266"/>
+      <c r="BE9" s="266"/>
       <c r="BF9" s="13"/>
-      <c r="BG9" s="185"/>
-      <c r="BH9" s="185"/>
+      <c r="BG9" s="267"/>
+      <c r="BH9" s="267"/>
     </row>
     <row r="10" spans="1:60" ht="15" customHeight="1">
-      <c r="A10" s="178"/>
-      <c r="B10" s="186"/>
-      <c r="C10" s="186"/>
-      <c r="D10" s="186"/>
-      <c r="E10" s="186"/>
-      <c r="F10" s="186"/>
-      <c r="G10" s="186"/>
-      <c r="H10" s="186"/>
-      <c r="I10" s="186"/>
-      <c r="J10" s="186"/>
-      <c r="K10" s="186"/>
-      <c r="L10" s="190"/>
-      <c r="M10" s="191"/>
-      <c r="N10" s="191"/>
-      <c r="O10" s="191"/>
-      <c r="P10" s="191"/>
-      <c r="Q10" s="191"/>
-      <c r="R10" s="191"/>
-      <c r="S10" s="191"/>
-      <c r="T10" s="192"/>
+      <c r="A10" s="260"/>
+      <c r="B10" s="253"/>
+      <c r="C10" s="253"/>
+      <c r="D10" s="253"/>
+      <c r="E10" s="253"/>
+      <c r="F10" s="253"/>
+      <c r="G10" s="253"/>
+      <c r="H10" s="253"/>
+      <c r="I10" s="253"/>
+      <c r="J10" s="253"/>
+      <c r="K10" s="253"/>
+      <c r="L10" s="273"/>
+      <c r="M10" s="274"/>
+      <c r="N10" s="274"/>
+      <c r="O10" s="274"/>
+      <c r="P10" s="274"/>
+      <c r="Q10" s="274"/>
+      <c r="R10" s="274"/>
+      <c r="S10" s="274"/>
+      <c r="T10" s="275"/>
       <c r="U10" s="13"/>
-      <c r="V10" s="190"/>
-      <c r="W10" s="191"/>
-      <c r="X10" s="191"/>
-      <c r="Y10" s="191"/>
-      <c r="Z10" s="191"/>
-      <c r="AA10" s="191"/>
-      <c r="AB10" s="191"/>
-      <c r="AC10" s="192"/>
-      <c r="AD10" s="186"/>
-      <c r="AE10" s="186"/>
-      <c r="AF10" s="186"/>
-      <c r="AG10" s="186"/>
-      <c r="AH10" s="186"/>
-      <c r="AI10" s="186"/>
-      <c r="AJ10" s="186"/>
-      <c r="AK10" s="186"/>
-      <c r="AL10" s="186"/>
+      <c r="V10" s="273"/>
+      <c r="W10" s="274"/>
+      <c r="X10" s="274"/>
+      <c r="Y10" s="274"/>
+      <c r="Z10" s="274"/>
+      <c r="AA10" s="274"/>
+      <c r="AB10" s="274"/>
+      <c r="AC10" s="275"/>
+      <c r="AD10" s="253"/>
+      <c r="AE10" s="253"/>
+      <c r="AF10" s="253"/>
+      <c r="AG10" s="253"/>
+      <c r="AH10" s="253"/>
+      <c r="AI10" s="253"/>
+      <c r="AJ10" s="253"/>
+      <c r="AK10" s="253"/>
+      <c r="AL10" s="253"/>
       <c r="AM10" s="3"/>
-      <c r="AN10" s="183" t="s">
+      <c r="AN10" s="258" t="s">
         <v>18</v>
       </c>
-      <c r="AO10" s="183"/>
-      <c r="AP10" s="183"/>
-      <c r="AQ10" s="184"/>
-      <c r="AR10" s="183" t="s">
+      <c r="AO10" s="258"/>
+      <c r="AP10" s="258"/>
+      <c r="AQ10" s="265"/>
+      <c r="AR10" s="258" t="s">
         <v>19</v>
       </c>
-      <c r="AS10" s="183"/>
-      <c r="AT10" s="183" t="s">
+      <c r="AS10" s="258"/>
+      <c r="AT10" s="258" t="s">
         <v>20</v>
       </c>
-      <c r="AU10" s="183"/>
-      <c r="AV10" s="183">
+      <c r="AU10" s="258"/>
+      <c r="AV10" s="258">
         <v>1</v>
       </c>
-      <c r="AW10" s="183"/>
-      <c r="AX10" s="183">
+      <c r="AW10" s="258"/>
+      <c r="AX10" s="258">
         <v>2</v>
       </c>
-      <c r="AY10" s="183"/>
-      <c r="AZ10" s="183">
+      <c r="AY10" s="258"/>
+      <c r="AZ10" s="258">
         <v>3</v>
       </c>
-      <c r="BA10" s="183"/>
-      <c r="BB10" s="273" t="s">
+      <c r="BA10" s="258"/>
+      <c r="BB10" s="259" t="s">
         <v>21</v>
       </c>
-      <c r="BC10" s="273"/>
-      <c r="BD10" s="183" t="s">
+      <c r="BC10" s="259"/>
+      <c r="BD10" s="258" t="s">
         <v>22</v>
       </c>
-      <c r="BE10" s="183"/>
+      <c r="BE10" s="258"/>
       <c r="BF10" s="13"/>
-      <c r="BG10" s="185"/>
-      <c r="BH10" s="185"/>
+      <c r="BG10" s="267"/>
+      <c r="BH10" s="267"/>
     </row>
     <row r="11" spans="1:60" ht="3" customHeight="1">
-      <c r="A11" s="178"/>
+      <c r="A11" s="260"/>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
@@ -2932,151 +2932,151 @@
       <c r="BD11" s="17"/>
       <c r="BE11" s="13"/>
       <c r="BF11" s="13"/>
-      <c r="BG11" s="185"/>
-      <c r="BH11" s="185"/>
+      <c r="BG11" s="267"/>
+      <c r="BH11" s="267"/>
     </row>
     <row r="12" spans="1:60" ht="9.9" customHeight="1">
-      <c r="A12" s="178"/>
-      <c r="B12" s="193" t="s">
+      <c r="A12" s="260"/>
+      <c r="B12" s="236" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="193"/>
-      <c r="D12" s="193"/>
-      <c r="E12" s="193"/>
-      <c r="F12" s="193"/>
-      <c r="G12" s="193"/>
-      <c r="H12" s="193"/>
-      <c r="I12" s="193"/>
-      <c r="J12" s="193"/>
-      <c r="K12" s="193"/>
-      <c r="L12" s="193" t="s">
+      <c r="C12" s="236"/>
+      <c r="D12" s="236"/>
+      <c r="E12" s="236"/>
+      <c r="F12" s="236"/>
+      <c r="G12" s="236"/>
+      <c r="H12" s="236"/>
+      <c r="I12" s="236"/>
+      <c r="J12" s="236"/>
+      <c r="K12" s="236"/>
+      <c r="L12" s="236" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="193"/>
-      <c r="N12" s="193"/>
-      <c r="O12" s="193"/>
-      <c r="P12" s="193"/>
-      <c r="Q12" s="193"/>
-      <c r="R12" s="193" t="s">
+      <c r="M12" s="236"/>
+      <c r="N12" s="236"/>
+      <c r="O12" s="236"/>
+      <c r="P12" s="236"/>
+      <c r="Q12" s="236"/>
+      <c r="R12" s="236" t="s">
         <v>25</v>
       </c>
-      <c r="S12" s="193"/>
-      <c r="T12" s="193"/>
-      <c r="U12" s="193"/>
-      <c r="V12" s="193"/>
-      <c r="W12" s="193"/>
-      <c r="X12" s="193"/>
-      <c r="Y12" s="193"/>
-      <c r="Z12" s="193"/>
-      <c r="AA12" s="193"/>
-      <c r="AB12" s="193"/>
-      <c r="AC12" s="193"/>
-      <c r="AD12" s="193"/>
-      <c r="AE12" s="193"/>
-      <c r="AF12" s="193"/>
-      <c r="AG12" s="193"/>
-      <c r="AH12" s="193"/>
-      <c r="AI12" s="193"/>
-      <c r="AJ12" s="193"/>
-      <c r="AK12" s="193"/>
-      <c r="AL12" s="213" t="s">
+      <c r="S12" s="236"/>
+      <c r="T12" s="236"/>
+      <c r="U12" s="236"/>
+      <c r="V12" s="236"/>
+      <c r="W12" s="236"/>
+      <c r="X12" s="236"/>
+      <c r="Y12" s="236"/>
+      <c r="Z12" s="236"/>
+      <c r="AA12" s="236"/>
+      <c r="AB12" s="236"/>
+      <c r="AC12" s="236"/>
+      <c r="AD12" s="236"/>
+      <c r="AE12" s="236"/>
+      <c r="AF12" s="236"/>
+      <c r="AG12" s="236"/>
+      <c r="AH12" s="236"/>
+      <c r="AI12" s="236"/>
+      <c r="AJ12" s="236"/>
+      <c r="AK12" s="236"/>
+      <c r="AL12" s="237" t="s">
         <v>26</v>
       </c>
-      <c r="AM12" s="214"/>
-      <c r="AN12" s="214"/>
-      <c r="AO12" s="214"/>
-      <c r="AP12" s="214"/>
-      <c r="AQ12" s="214"/>
-      <c r="AR12" s="215"/>
-      <c r="AS12" s="213" t="s">
+      <c r="AM12" s="238"/>
+      <c r="AN12" s="238"/>
+      <c r="AO12" s="238"/>
+      <c r="AP12" s="238"/>
+      <c r="AQ12" s="238"/>
+      <c r="AR12" s="239"/>
+      <c r="AS12" s="237" t="s">
         <v>27</v>
       </c>
-      <c r="AT12" s="214"/>
-      <c r="AU12" s="214"/>
-      <c r="AV12" s="214"/>
-      <c r="AW12" s="214"/>
-      <c r="AX12" s="214"/>
-      <c r="AY12" s="214"/>
-      <c r="AZ12" s="214"/>
-      <c r="BA12" s="214"/>
-      <c r="BB12" s="214"/>
-      <c r="BC12" s="214"/>
-      <c r="BD12" s="214"/>
-      <c r="BE12" s="215"/>
+      <c r="AT12" s="238"/>
+      <c r="AU12" s="238"/>
+      <c r="AV12" s="238"/>
+      <c r="AW12" s="238"/>
+      <c r="AX12" s="238"/>
+      <c r="AY12" s="238"/>
+      <c r="AZ12" s="238"/>
+      <c r="BA12" s="238"/>
+      <c r="BB12" s="238"/>
+      <c r="BC12" s="238"/>
+      <c r="BD12" s="238"/>
+      <c r="BE12" s="239"/>
       <c r="BF12" s="13"/>
-      <c r="BG12" s="185"/>
-      <c r="BH12" s="185"/>
+      <c r="BG12" s="267"/>
+      <c r="BH12" s="267"/>
     </row>
     <row r="13" spans="1:60" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="178"/>
-      <c r="B13" s="202"/>
-      <c r="C13" s="203"/>
-      <c r="D13" s="203"/>
-      <c r="E13" s="203"/>
-      <c r="F13" s="203"/>
-      <c r="G13" s="203"/>
-      <c r="H13" s="203"/>
-      <c r="I13" s="203"/>
-      <c r="J13" s="203"/>
-      <c r="K13" s="204"/>
-      <c r="L13" s="205"/>
-      <c r="M13" s="206"/>
-      <c r="N13" s="206"/>
-      <c r="O13" s="206"/>
-      <c r="P13" s="206"/>
-      <c r="Q13" s="207"/>
-      <c r="R13" s="186" t="s">
+      <c r="A13" s="260"/>
+      <c r="B13" s="250"/>
+      <c r="C13" s="251"/>
+      <c r="D13" s="251"/>
+      <c r="E13" s="251"/>
+      <c r="F13" s="251"/>
+      <c r="G13" s="251"/>
+      <c r="H13" s="251"/>
+      <c r="I13" s="251"/>
+      <c r="J13" s="251"/>
+      <c r="K13" s="252"/>
+      <c r="L13" s="228"/>
+      <c r="M13" s="229"/>
+      <c r="N13" s="229"/>
+      <c r="O13" s="229"/>
+      <c r="P13" s="229"/>
+      <c r="Q13" s="230"/>
+      <c r="R13" s="253" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="186"/>
-      <c r="T13" s="186"/>
-      <c r="U13" s="186"/>
-      <c r="V13" s="186"/>
-      <c r="W13" s="186"/>
-      <c r="X13" s="186"/>
-      <c r="Y13" s="186"/>
-      <c r="Z13" s="186"/>
-      <c r="AA13" s="186"/>
-      <c r="AB13" s="186"/>
-      <c r="AC13" s="186"/>
-      <c r="AD13" s="186"/>
-      <c r="AE13" s="186"/>
-      <c r="AF13" s="186"/>
-      <c r="AG13" s="186"/>
-      <c r="AH13" s="186"/>
-      <c r="AI13" s="186"/>
-      <c r="AJ13" s="186"/>
-      <c r="AK13" s="186"/>
-      <c r="AL13" s="208">
+      <c r="S13" s="253"/>
+      <c r="T13" s="253"/>
+      <c r="U13" s="253"/>
+      <c r="V13" s="253"/>
+      <c r="W13" s="253"/>
+      <c r="X13" s="253"/>
+      <c r="Y13" s="253"/>
+      <c r="Z13" s="253"/>
+      <c r="AA13" s="253"/>
+      <c r="AB13" s="253"/>
+      <c r="AC13" s="253"/>
+      <c r="AD13" s="253"/>
+      <c r="AE13" s="253"/>
+      <c r="AF13" s="253"/>
+      <c r="AG13" s="253"/>
+      <c r="AH13" s="253"/>
+      <c r="AI13" s="253"/>
+      <c r="AJ13" s="253"/>
+      <c r="AK13" s="253"/>
+      <c r="AL13" s="254">
         <v>5194</v>
       </c>
-      <c r="AM13" s="208"/>
-      <c r="AN13" s="208"/>
-      <c r="AO13" s="208"/>
-      <c r="AP13" s="208"/>
-      <c r="AQ13" s="208"/>
-      <c r="AR13" s="208"/>
-      <c r="AS13" s="209" t="s">
+      <c r="AM13" s="254"/>
+      <c r="AN13" s="254"/>
+      <c r="AO13" s="254"/>
+      <c r="AP13" s="254"/>
+      <c r="AQ13" s="254"/>
+      <c r="AR13" s="254"/>
+      <c r="AS13" s="255" t="s">
         <v>29</v>
       </c>
-      <c r="AT13" s="210"/>
-      <c r="AU13" s="210"/>
-      <c r="AV13" s="210"/>
-      <c r="AW13" s="210"/>
-      <c r="AX13" s="210"/>
-      <c r="AY13" s="210"/>
-      <c r="AZ13" s="210"/>
-      <c r="BA13" s="210"/>
-      <c r="BB13" s="210"/>
-      <c r="BC13" s="210"/>
-      <c r="BD13" s="210"/>
-      <c r="BE13" s="211"/>
+      <c r="AT13" s="256"/>
+      <c r="AU13" s="256"/>
+      <c r="AV13" s="256"/>
+      <c r="AW13" s="256"/>
+      <c r="AX13" s="256"/>
+      <c r="AY13" s="256"/>
+      <c r="AZ13" s="256"/>
+      <c r="BA13" s="256"/>
+      <c r="BB13" s="256"/>
+      <c r="BC13" s="256"/>
+      <c r="BD13" s="256"/>
+      <c r="BE13" s="257"/>
       <c r="BF13" s="13"/>
-      <c r="BG13" s="185"/>
-      <c r="BH13" s="185"/>
+      <c r="BG13" s="267"/>
+      <c r="BH13" s="267"/>
     </row>
     <row r="14" spans="1:60" ht="3" customHeight="1">
-      <c r="A14" s="178"/>
+      <c r="A14" s="260"/>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
@@ -3134,11 +3134,11 @@
       <c r="BD14" s="18"/>
       <c r="BE14" s="18"/>
       <c r="BF14" s="13"/>
-      <c r="BG14" s="185"/>
-      <c r="BH14" s="185"/>
+      <c r="BG14" s="267"/>
+      <c r="BH14" s="267"/>
     </row>
     <row r="15" spans="1:60" ht="9.9" customHeight="1">
-      <c r="A15" s="178"/>
+      <c r="A15" s="260"/>
       <c r="B15" s="19" t="s">
         <v>30</v>
       </c>
@@ -3186,27 +3186,27 @@
       <c r="AP15" s="20"/>
       <c r="AQ15" s="20"/>
       <c r="AR15" s="20"/>
-      <c r="AS15" s="212" t="s">
+      <c r="AS15" s="235" t="s">
         <v>32</v>
       </c>
-      <c r="AT15" s="212"/>
-      <c r="AU15" s="212"/>
-      <c r="AV15" s="212"/>
-      <c r="AW15" s="212"/>
-      <c r="AX15" s="212"/>
-      <c r="AY15" s="212"/>
-      <c r="AZ15" s="212"/>
-      <c r="BA15" s="212"/>
-      <c r="BB15" s="212"/>
-      <c r="BC15" s="212"/>
-      <c r="BD15" s="212"/>
-      <c r="BE15" s="212"/>
+      <c r="AT15" s="235"/>
+      <c r="AU15" s="235"/>
+      <c r="AV15" s="235"/>
+      <c r="AW15" s="235"/>
+      <c r="AX15" s="235"/>
+      <c r="AY15" s="235"/>
+      <c r="AZ15" s="235"/>
+      <c r="BA15" s="235"/>
+      <c r="BB15" s="235"/>
+      <c r="BC15" s="235"/>
+      <c r="BD15" s="235"/>
+      <c r="BE15" s="235"/>
       <c r="BF15" s="13"/>
-      <c r="BG15" s="185"/>
-      <c r="BH15" s="185"/>
+      <c r="BG15" s="267"/>
+      <c r="BH15" s="267"/>
     </row>
     <row r="16" spans="1:60" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="178"/>
+      <c r="A16" s="260"/>
       <c r="B16" s="23"/>
       <c r="C16" s="24"/>
       <c r="D16" s="25" t="s">
@@ -3254,36 +3254,36 @@
       <c r="AP16" s="24"/>
       <c r="AQ16" s="24"/>
       <c r="AR16" s="24"/>
-      <c r="AS16" s="216"/>
-      <c r="AT16" s="216"/>
-      <c r="AU16" s="216"/>
-      <c r="AV16" s="216"/>
-      <c r="AW16" s="216"/>
-      <c r="AX16" s="216"/>
-      <c r="AY16" s="216"/>
-      <c r="AZ16" s="216"/>
-      <c r="BA16" s="216"/>
-      <c r="BB16" s="216"/>
-      <c r="BC16" s="216"/>
-      <c r="BD16" s="216"/>
-      <c r="BE16" s="216"/>
+      <c r="AS16" s="240"/>
+      <c r="AT16" s="240"/>
+      <c r="AU16" s="240"/>
+      <c r="AV16" s="240"/>
+      <c r="AW16" s="240"/>
+      <c r="AX16" s="240"/>
+      <c r="AY16" s="240"/>
+      <c r="AZ16" s="240"/>
+      <c r="BA16" s="240"/>
+      <c r="BB16" s="240"/>
+      <c r="BC16" s="240"/>
+      <c r="BD16" s="240"/>
+      <c r="BE16" s="240"/>
       <c r="BF16" s="13"/>
       <c r="BG16" s="9"/>
       <c r="BH16" s="9"/>
     </row>
     <row r="17" spans="1:60" ht="14.25" customHeight="1">
-      <c r="A17" s="178"/>
-      <c r="B17" s="217" t="s">
+      <c r="A17" s="260"/>
+      <c r="B17" s="241" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="217"/>
-      <c r="D17" s="217"/>
-      <c r="E17" s="217"/>
-      <c r="F17" s="217"/>
-      <c r="G17" s="217"/>
-      <c r="H17" s="217"/>
-      <c r="I17" s="217"/>
-      <c r="J17" s="217"/>
+      <c r="C17" s="241"/>
+      <c r="D17" s="241"/>
+      <c r="E17" s="241"/>
+      <c r="F17" s="241"/>
+      <c r="G17" s="241"/>
+      <c r="H17" s="241"/>
+      <c r="I17" s="241"/>
+      <c r="J17" s="241"/>
       <c r="K17" s="13"/>
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
@@ -3336,145 +3336,145 @@
       <c r="BH17" s="9"/>
     </row>
     <row r="18" spans="1:60" ht="9.9" customHeight="1">
-      <c r="A18" s="178"/>
-      <c r="B18" s="213" t="s">
+      <c r="A18" s="260"/>
+      <c r="B18" s="237" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="214"/>
-      <c r="D18" s="214"/>
-      <c r="E18" s="214"/>
-      <c r="F18" s="214"/>
-      <c r="G18" s="215"/>
-      <c r="H18" s="213" t="s">
+      <c r="C18" s="238"/>
+      <c r="D18" s="238"/>
+      <c r="E18" s="238"/>
+      <c r="F18" s="238"/>
+      <c r="G18" s="239"/>
+      <c r="H18" s="237" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="214"/>
-      <c r="J18" s="214"/>
-      <c r="K18" s="214"/>
-      <c r="L18" s="214"/>
-      <c r="M18" s="214"/>
-      <c r="N18" s="214"/>
-      <c r="O18" s="215"/>
-      <c r="P18" s="213" t="s">
+      <c r="I18" s="238"/>
+      <c r="J18" s="238"/>
+      <c r="K18" s="238"/>
+      <c r="L18" s="238"/>
+      <c r="M18" s="238"/>
+      <c r="N18" s="238"/>
+      <c r="O18" s="239"/>
+      <c r="P18" s="237" t="s">
         <v>38</v>
       </c>
-      <c r="Q18" s="214"/>
-      <c r="R18" s="214"/>
-      <c r="S18" s="214"/>
-      <c r="T18" s="214"/>
-      <c r="U18" s="214"/>
-      <c r="V18" s="214"/>
-      <c r="W18" s="215"/>
+      <c r="Q18" s="238"/>
+      <c r="R18" s="238"/>
+      <c r="S18" s="238"/>
+      <c r="T18" s="238"/>
+      <c r="U18" s="238"/>
+      <c r="V18" s="238"/>
+      <c r="W18" s="239"/>
       <c r="X18" s="6"/>
-      <c r="Y18" s="213" t="s">
+      <c r="Y18" s="237" t="s">
         <v>36</v>
       </c>
-      <c r="Z18" s="214"/>
-      <c r="AA18" s="214"/>
-      <c r="AB18" s="214"/>
-      <c r="AC18" s="214"/>
-      <c r="AD18" s="215"/>
-      <c r="AE18" s="213" t="s">
+      <c r="Z18" s="238"/>
+      <c r="AA18" s="238"/>
+      <c r="AB18" s="238"/>
+      <c r="AC18" s="238"/>
+      <c r="AD18" s="239"/>
+      <c r="AE18" s="237" t="s">
         <v>37</v>
       </c>
-      <c r="AF18" s="214"/>
-      <c r="AG18" s="214"/>
-      <c r="AH18" s="214"/>
-      <c r="AI18" s="214"/>
-      <c r="AJ18" s="214"/>
-      <c r="AK18" s="214"/>
-      <c r="AL18" s="215"/>
-      <c r="AM18" s="213" t="s">
+      <c r="AF18" s="238"/>
+      <c r="AG18" s="238"/>
+      <c r="AH18" s="238"/>
+      <c r="AI18" s="238"/>
+      <c r="AJ18" s="238"/>
+      <c r="AK18" s="238"/>
+      <c r="AL18" s="239"/>
+      <c r="AM18" s="237" t="s">
         <v>38</v>
       </c>
-      <c r="AN18" s="214"/>
-      <c r="AO18" s="214"/>
-      <c r="AP18" s="214"/>
-      <c r="AQ18" s="214"/>
-      <c r="AR18" s="214"/>
-      <c r="AS18" s="214"/>
-      <c r="AT18" s="215"/>
+      <c r="AN18" s="238"/>
+      <c r="AO18" s="238"/>
+      <c r="AP18" s="238"/>
+      <c r="AQ18" s="238"/>
+      <c r="AR18" s="238"/>
+      <c r="AS18" s="238"/>
+      <c r="AT18" s="239"/>
       <c r="AU18" s="6"/>
-      <c r="AV18" s="213" t="s">
+      <c r="AV18" s="237" t="s">
         <v>39</v>
       </c>
-      <c r="AW18" s="214"/>
-      <c r="AX18" s="214"/>
-      <c r="AY18" s="214"/>
-      <c r="AZ18" s="214"/>
-      <c r="BA18" s="214"/>
-      <c r="BB18" s="214"/>
-      <c r="BC18" s="214"/>
-      <c r="BD18" s="214"/>
-      <c r="BE18" s="215"/>
+      <c r="AW18" s="238"/>
+      <c r="AX18" s="238"/>
+      <c r="AY18" s="238"/>
+      <c r="AZ18" s="238"/>
+      <c r="BA18" s="238"/>
+      <c r="BB18" s="238"/>
+      <c r="BC18" s="238"/>
+      <c r="BD18" s="238"/>
+      <c r="BE18" s="239"/>
       <c r="BF18" s="13"/>
       <c r="BG18" s="9"/>
       <c r="BH18" s="9"/>
     </row>
     <row r="19" spans="1:60" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="178"/>
-      <c r="B19" s="205"/>
-      <c r="C19" s="206"/>
-      <c r="D19" s="206"/>
-      <c r="E19" s="206"/>
-      <c r="F19" s="206"/>
-      <c r="G19" s="207"/>
-      <c r="H19" s="205"/>
-      <c r="I19" s="206"/>
-      <c r="J19" s="206"/>
-      <c r="K19" s="206"/>
-      <c r="L19" s="206"/>
-      <c r="M19" s="206"/>
-      <c r="N19" s="206"/>
-      <c r="O19" s="207"/>
-      <c r="P19" s="205"/>
-      <c r="Q19" s="206"/>
-      <c r="R19" s="206"/>
-      <c r="S19" s="206"/>
-      <c r="T19" s="206"/>
-      <c r="U19" s="206"/>
-      <c r="V19" s="206"/>
-      <c r="W19" s="207"/>
+      <c r="A19" s="260"/>
+      <c r="B19" s="228"/>
+      <c r="C19" s="229"/>
+      <c r="D19" s="229"/>
+      <c r="E19" s="229"/>
+      <c r="F19" s="229"/>
+      <c r="G19" s="230"/>
+      <c r="H19" s="228"/>
+      <c r="I19" s="229"/>
+      <c r="J19" s="229"/>
+      <c r="K19" s="229"/>
+      <c r="L19" s="229"/>
+      <c r="M19" s="229"/>
+      <c r="N19" s="229"/>
+      <c r="O19" s="230"/>
+      <c r="P19" s="228"/>
+      <c r="Q19" s="229"/>
+      <c r="R19" s="229"/>
+      <c r="S19" s="229"/>
+      <c r="T19" s="229"/>
+      <c r="U19" s="229"/>
+      <c r="V19" s="229"/>
+      <c r="W19" s="230"/>
       <c r="X19" s="10"/>
-      <c r="Y19" s="205"/>
-      <c r="Z19" s="206"/>
-      <c r="AA19" s="206"/>
-      <c r="AB19" s="206"/>
-      <c r="AC19" s="206"/>
-      <c r="AD19" s="207"/>
-      <c r="AE19" s="205"/>
-      <c r="AF19" s="206"/>
-      <c r="AG19" s="206"/>
-      <c r="AH19" s="206"/>
-      <c r="AI19" s="206"/>
-      <c r="AJ19" s="206"/>
-      <c r="AK19" s="206"/>
-      <c r="AL19" s="207"/>
-      <c r="AM19" s="205"/>
-      <c r="AN19" s="206"/>
-      <c r="AO19" s="206"/>
-      <c r="AP19" s="206"/>
-      <c r="AQ19" s="206"/>
-      <c r="AR19" s="206"/>
-      <c r="AS19" s="206"/>
-      <c r="AT19" s="207"/>
+      <c r="Y19" s="228"/>
+      <c r="Z19" s="229"/>
+      <c r="AA19" s="229"/>
+      <c r="AB19" s="229"/>
+      <c r="AC19" s="229"/>
+      <c r="AD19" s="230"/>
+      <c r="AE19" s="228"/>
+      <c r="AF19" s="229"/>
+      <c r="AG19" s="229"/>
+      <c r="AH19" s="229"/>
+      <c r="AI19" s="229"/>
+      <c r="AJ19" s="229"/>
+      <c r="AK19" s="229"/>
+      <c r="AL19" s="230"/>
+      <c r="AM19" s="228"/>
+      <c r="AN19" s="229"/>
+      <c r="AO19" s="229"/>
+      <c r="AP19" s="229"/>
+      <c r="AQ19" s="229"/>
+      <c r="AR19" s="229"/>
+      <c r="AS19" s="229"/>
+      <c r="AT19" s="230"/>
       <c r="AU19" s="10"/>
-      <c r="AV19" s="205"/>
-      <c r="AW19" s="206"/>
-      <c r="AX19" s="206"/>
-      <c r="AY19" s="206"/>
-      <c r="AZ19" s="206"/>
-      <c r="BA19" s="206"/>
-      <c r="BB19" s="206"/>
-      <c r="BC19" s="206"/>
-      <c r="BD19" s="206"/>
-      <c r="BE19" s="207"/>
+      <c r="AV19" s="228"/>
+      <c r="AW19" s="229"/>
+      <c r="AX19" s="229"/>
+      <c r="AY19" s="229"/>
+      <c r="AZ19" s="229"/>
+      <c r="BA19" s="229"/>
+      <c r="BB19" s="229"/>
+      <c r="BC19" s="229"/>
+      <c r="BD19" s="229"/>
+      <c r="BE19" s="230"/>
       <c r="BF19" s="13"/>
       <c r="BG19" s="9"/>
       <c r="BH19" s="9"/>
     </row>
     <row r="20" spans="1:60" ht="3" customHeight="1">
-      <c r="A20" s="178"/>
+      <c r="A20" s="260"/>
       <c r="B20" s="26"/>
       <c r="C20" s="26"/>
       <c r="D20" s="26"/>
@@ -3536,7 +3536,7 @@
       <c r="BH20" s="9"/>
     </row>
     <row r="21" spans="1:60" ht="9.9" customHeight="1">
-      <c r="A21" s="178"/>
+      <c r="A21" s="260"/>
       <c r="B21" s="17" t="s">
         <v>40</v>
       </c>
@@ -3600,7 +3600,7 @@
       <c r="BH21" s="28"/>
     </row>
     <row r="22" spans="1:60" ht="9.9" customHeight="1">
-      <c r="A22" s="178"/>
+      <c r="A22" s="260"/>
       <c r="B22" s="1" t="s">
         <v>41</v>
       </c>
@@ -3664,7 +3664,7 @@
       <c r="BH22" s="9"/>
     </row>
     <row r="23" spans="1:60" s="33" customFormat="1" ht="9.9" customHeight="1">
-      <c r="A23" s="178"/>
+      <c r="A23" s="260"/>
       <c r="B23" s="30"/>
       <c r="C23" s="30"/>
       <c r="D23" s="30"/>
@@ -3728,7 +3728,7 @@
       <c r="BH23" s="32"/>
     </row>
     <row r="24" spans="1:60" s="33" customFormat="1" ht="3" customHeight="1">
-      <c r="A24" s="178"/>
+      <c r="A24" s="260"/>
       <c r="B24" s="30"/>
       <c r="C24" s="30"/>
       <c r="D24" s="30"/>
@@ -3790,7 +3790,7 @@
       <c r="BH24" s="32"/>
     </row>
     <row r="25" spans="1:60" s="33" customFormat="1" ht="9.9" customHeight="1">
-      <c r="A25" s="178"/>
+      <c r="A25" s="260"/>
       <c r="B25" s="30"/>
       <c r="C25" s="30"/>
       <c r="D25" s="30"/>
@@ -3805,44 +3805,44 @@
       <c r="M25" s="36"/>
       <c r="N25" s="36"/>
       <c r="O25" s="36"/>
-      <c r="P25" s="218" t="s">
+      <c r="P25" s="231" t="s">
         <v>43</v>
       </c>
-      <c r="Q25" s="218"/>
-      <c r="R25" s="218"/>
-      <c r="S25" s="218"/>
-      <c r="T25" s="218"/>
-      <c r="U25" s="218"/>
-      <c r="V25" s="218"/>
-      <c r="W25" s="218"/>
-      <c r="X25" s="218" t="s">
+      <c r="Q25" s="231"/>
+      <c r="R25" s="231"/>
+      <c r="S25" s="231"/>
+      <c r="T25" s="231"/>
+      <c r="U25" s="231"/>
+      <c r="V25" s="231"/>
+      <c r="W25" s="231"/>
+      <c r="X25" s="231" t="s">
         <v>44</v>
       </c>
-      <c r="Y25" s="218"/>
-      <c r="Z25" s="218"/>
-      <c r="AA25" s="218"/>
-      <c r="AB25" s="218"/>
-      <c r="AC25" s="218"/>
-      <c r="AD25" s="218"/>
-      <c r="AE25" s="218" t="s">
+      <c r="Y25" s="231"/>
+      <c r="Z25" s="231"/>
+      <c r="AA25" s="231"/>
+      <c r="AB25" s="231"/>
+      <c r="AC25" s="231"/>
+      <c r="AD25" s="231"/>
+      <c r="AE25" s="231" t="s">
         <v>45</v>
       </c>
-      <c r="AF25" s="218"/>
-      <c r="AG25" s="218"/>
-      <c r="AH25" s="218"/>
-      <c r="AI25" s="218"/>
-      <c r="AJ25" s="218"/>
-      <c r="AK25" s="218"/>
-      <c r="AL25" s="218" t="s">
+      <c r="AF25" s="231"/>
+      <c r="AG25" s="231"/>
+      <c r="AH25" s="231"/>
+      <c r="AI25" s="231"/>
+      <c r="AJ25" s="231"/>
+      <c r="AK25" s="231"/>
+      <c r="AL25" s="231" t="s">
         <v>46</v>
       </c>
-      <c r="AM25" s="218"/>
-      <c r="AN25" s="218"/>
-      <c r="AO25" s="218"/>
-      <c r="AP25" s="218"/>
-      <c r="AQ25" s="218"/>
-      <c r="AR25" s="218"/>
-      <c r="AS25" s="218"/>
+      <c r="AM25" s="231"/>
+      <c r="AN25" s="231"/>
+      <c r="AO25" s="231"/>
+      <c r="AP25" s="231"/>
+      <c r="AQ25" s="231"/>
+      <c r="AR25" s="231"/>
+      <c r="AS25" s="231"/>
       <c r="AT25" s="34"/>
       <c r="AU25" s="30"/>
       <c r="AV25" s="30"/>
@@ -3860,7 +3860,7 @@
       <c r="BH25" s="32"/>
     </row>
     <row r="26" spans="1:60" s="33" customFormat="1" ht="3" customHeight="1">
-      <c r="A26" s="178"/>
+      <c r="A26" s="260"/>
       <c r="B26" s="30"/>
       <c r="C26" s="30"/>
       <c r="D26" s="30"/>
@@ -3922,7 +3922,7 @@
       <c r="BH26" s="32"/>
     </row>
     <row r="27" spans="1:60" s="33" customFormat="1" ht="9.9" customHeight="1">
-      <c r="A27" s="178"/>
+      <c r="A27" s="260"/>
       <c r="B27" s="38"/>
       <c r="C27" s="38"/>
       <c r="D27" s="34"/>
@@ -3988,7 +3988,7 @@
       <c r="BH27" s="47"/>
     </row>
     <row r="28" spans="1:60" s="33" customFormat="1" ht="9.9" customHeight="1">
-      <c r="A28" s="178"/>
+      <c r="A28" s="260"/>
       <c r="B28" s="36"/>
       <c r="C28" s="36"/>
       <c r="D28" s="36"/>
@@ -4019,10 +4019,10 @@
       <c r="W28" s="54"/>
       <c r="X28" s="54"/>
       <c r="Y28" s="41"/>
-      <c r="Z28" s="219"/>
-      <c r="AA28" s="219"/>
+      <c r="Z28" s="232"/>
+      <c r="AA28" s="232"/>
       <c r="AB28" s="55"/>
-      <c r="AC28" s="220" t="s">
+      <c r="AC28" s="233" t="s">
         <v>52</v>
       </c>
       <c r="AD28" s="38"/>
@@ -4054,15 +4054,15 @@
       <c r="BB28" s="54"/>
       <c r="BC28" s="54"/>
       <c r="BD28" s="41"/>
-      <c r="BE28" s="219"/>
-      <c r="BF28" s="219"/>
+      <c r="BE28" s="232"/>
+      <c r="BF28" s="232"/>
       <c r="BG28" s="57"/>
-      <c r="BH28" s="228" t="s">
+      <c r="BH28" s="224" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:60" s="33" customFormat="1" ht="9.9" customHeight="1">
-      <c r="A29" s="178"/>
+      <c r="A29" s="260"/>
       <c r="B29" s="58"/>
       <c r="C29" s="58"/>
       <c r="D29" s="58"/>
@@ -4087,12 +4087,12 @@
       <c r="U29" s="61"/>
       <c r="V29" s="41"/>
       <c r="W29" s="62"/>
-      <c r="X29" s="230"/>
-      <c r="Y29" s="230"/>
+      <c r="X29" s="226"/>
+      <c r="Y29" s="226"/>
       <c r="Z29" s="63"/>
       <c r="AA29" s="46"/>
       <c r="AB29" s="64"/>
-      <c r="AC29" s="220"/>
+      <c r="AC29" s="233"/>
       <c r="AD29" s="60"/>
       <c r="AE29" s="60"/>
       <c r="AF29" s="60"/>
@@ -4120,15 +4120,15 @@
       <c r="AZ29" s="61"/>
       <c r="BA29" s="41"/>
       <c r="BB29" s="62"/>
-      <c r="BC29" s="230"/>
-      <c r="BD29" s="230"/>
+      <c r="BC29" s="226"/>
+      <c r="BD29" s="226"/>
       <c r="BE29" s="63"/>
       <c r="BF29" s="46"/>
       <c r="BG29" s="65"/>
-      <c r="BH29" s="228"/>
+      <c r="BH29" s="224"/>
     </row>
     <row r="30" spans="1:60" ht="9.9" customHeight="1">
-      <c r="A30" s="178"/>
+      <c r="A30" s="260"/>
       <c r="B30" s="66"/>
       <c r="C30" s="58"/>
       <c r="D30" s="58"/>
@@ -4158,7 +4158,7 @@
       <c r="Z30" s="72"/>
       <c r="AA30" s="73"/>
       <c r="AB30" s="74"/>
-      <c r="AC30" s="221"/>
+      <c r="AC30" s="234"/>
       <c r="AD30" s="60"/>
       <c r="AE30" s="60"/>
       <c r="AF30" s="75"/>
@@ -4191,10 +4191,10 @@
       <c r="BE30" s="72"/>
       <c r="BF30" s="73"/>
       <c r="BG30" s="76"/>
-      <c r="BH30" s="229"/>
+      <c r="BH30" s="225"/>
     </row>
     <row r="31" spans="1:60" ht="11.1" customHeight="1">
-      <c r="A31" s="178"/>
+      <c r="A31" s="260"/>
       <c r="B31" s="77" t="s">
         <v>55</v>
       </c>
@@ -4280,7 +4280,7 @@
       <c r="BH31" s="90"/>
     </row>
     <row r="32" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A32" s="178"/>
+      <c r="A32" s="260"/>
       <c r="B32" s="91">
         <v>1</v>
       </c>
@@ -4307,22 +4307,22 @@
       <c r="U32" s="93"/>
       <c r="V32" s="93"/>
       <c r="W32" s="94"/>
-      <c r="X32" s="225" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y32" s="225" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z32" s="225" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA32" s="225" t="s">
-        <v>57</v>
-      </c>
-      <c r="AB32" s="225" t="s">
-        <v>57</v>
-      </c>
-      <c r="AC32" s="231" t="s">
+      <c r="X32" s="198" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y32" s="198" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z32" s="198" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA32" s="198" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB32" s="198" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC32" s="189" t="s">
         <v>58</v>
       </c>
       <c r="AD32" s="85"/>
@@ -4331,38 +4331,38 @@
       <c r="AG32" s="95">
         <v>7</v>
       </c>
-      <c r="AH32" s="233" t="s">
+      <c r="AH32" s="206" t="s">
         <v>59</v>
       </c>
-      <c r="AI32" s="233"/>
-      <c r="AJ32" s="233"/>
-      <c r="AK32" s="233"/>
-      <c r="AL32" s="233"/>
-      <c r="AM32" s="233"/>
-      <c r="AN32" s="233"/>
-      <c r="AO32" s="233"/>
-      <c r="AP32" s="233"/>
-      <c r="AQ32" s="233"/>
-      <c r="AR32" s="233"/>
-      <c r="AS32" s="233"/>
-      <c r="AT32" s="233"/>
-      <c r="AU32" s="233"/>
-      <c r="AV32" s="233"/>
-      <c r="AW32" s="233"/>
-      <c r="AX32" s="233"/>
-      <c r="AY32" s="233"/>
-      <c r="AZ32" s="233"/>
-      <c r="BA32" s="233"/>
-      <c r="BB32" s="233"/>
-      <c r="BC32" s="233"/>
-      <c r="BD32" s="233"/>
-      <c r="BE32" s="233"/>
-      <c r="BF32" s="233"/>
-      <c r="BG32" s="233"/>
-      <c r="BH32" s="234"/>
+      <c r="AI32" s="206"/>
+      <c r="AJ32" s="206"/>
+      <c r="AK32" s="206"/>
+      <c r="AL32" s="206"/>
+      <c r="AM32" s="206"/>
+      <c r="AN32" s="206"/>
+      <c r="AO32" s="206"/>
+      <c r="AP32" s="206"/>
+      <c r="AQ32" s="206"/>
+      <c r="AR32" s="206"/>
+      <c r="AS32" s="206"/>
+      <c r="AT32" s="206"/>
+      <c r="AU32" s="206"/>
+      <c r="AV32" s="206"/>
+      <c r="AW32" s="206"/>
+      <c r="AX32" s="206"/>
+      <c r="AY32" s="206"/>
+      <c r="AZ32" s="206"/>
+      <c r="BA32" s="206"/>
+      <c r="BB32" s="206"/>
+      <c r="BC32" s="206"/>
+      <c r="BD32" s="206"/>
+      <c r="BE32" s="206"/>
+      <c r="BF32" s="206"/>
+      <c r="BG32" s="206"/>
+      <c r="BH32" s="227"/>
     </row>
     <row r="33" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A33" s="178"/>
+      <c r="A33" s="260"/>
       <c r="B33" s="96"/>
       <c r="C33" s="67" t="s">
         <v>60</v>
@@ -4387,16 +4387,16 @@
       <c r="U33" s="97"/>
       <c r="V33" s="97"/>
       <c r="W33" s="98"/>
-      <c r="X33" s="226"/>
-      <c r="Y33" s="226"/>
-      <c r="Z33" s="226"/>
-      <c r="AA33" s="226"/>
-      <c r="AB33" s="226"/>
-      <c r="AC33" s="232"/>
+      <c r="X33" s="199"/>
+      <c r="Y33" s="199"/>
+      <c r="Z33" s="199"/>
+      <c r="AA33" s="199"/>
+      <c r="AB33" s="199"/>
+      <c r="AC33" s="190"/>
       <c r="AD33" s="85"/>
       <c r="AE33" s="86"/>
       <c r="AF33" s="87"/>
-      <c r="AG33" s="222" t="s">
+      <c r="AG33" s="202" t="s">
         <v>61</v>
       </c>
       <c r="AH33" s="99" t="s">
@@ -4422,25 +4422,25 @@
       <c r="AZ33" s="100"/>
       <c r="BA33" s="100"/>
       <c r="BB33" s="101"/>
-      <c r="BC33" s="225" t="s">
-        <v>57</v>
-      </c>
-      <c r="BD33" s="225" t="s">
-        <v>57</v>
-      </c>
-      <c r="BE33" s="225" t="s">
-        <v>57</v>
-      </c>
-      <c r="BF33" s="225" t="s">
-        <v>57</v>
-      </c>
-      <c r="BG33" s="235"/>
-      <c r="BH33" s="231" t="s">
+      <c r="BC33" s="198" t="s">
+        <v>57</v>
+      </c>
+      <c r="BD33" s="198" t="s">
+        <v>57</v>
+      </c>
+      <c r="BE33" s="198" t="s">
+        <v>57</v>
+      </c>
+      <c r="BF33" s="198" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG33" s="200"/>
+      <c r="BH33" s="189" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A34" s="178"/>
+      <c r="A34" s="260"/>
       <c r="B34" s="102">
         <v>2</v>
       </c>
@@ -4480,7 +4480,7 @@
       <c r="AD34" s="85"/>
       <c r="AE34" s="86"/>
       <c r="AF34" s="87"/>
-      <c r="AG34" s="223"/>
+      <c r="AG34" s="203"/>
       <c r="AH34" s="108" t="s">
         <v>65</v>
       </c>
@@ -4504,55 +4504,55 @@
       <c r="AZ34" s="109"/>
       <c r="BA34" s="109"/>
       <c r="BB34" s="110"/>
-      <c r="BC34" s="226"/>
-      <c r="BD34" s="226"/>
-      <c r="BE34" s="226"/>
-      <c r="BF34" s="226"/>
-      <c r="BG34" s="236"/>
-      <c r="BH34" s="232"/>
+      <c r="BC34" s="199"/>
+      <c r="BD34" s="199"/>
+      <c r="BE34" s="199"/>
+      <c r="BF34" s="199"/>
+      <c r="BG34" s="201"/>
+      <c r="BH34" s="190"/>
     </row>
     <row r="35" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A35" s="178"/>
+      <c r="A35" s="260"/>
       <c r="B35" s="91">
         <v>3</v>
       </c>
-      <c r="C35" s="243" t="s">
+      <c r="C35" s="219" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="243"/>
-      <c r="E35" s="243"/>
-      <c r="F35" s="243"/>
-      <c r="G35" s="243"/>
-      <c r="H35" s="243"/>
-      <c r="I35" s="243"/>
-      <c r="J35" s="243"/>
-      <c r="K35" s="243"/>
-      <c r="L35" s="243"/>
-      <c r="M35" s="243"/>
-      <c r="N35" s="243"/>
-      <c r="O35" s="243"/>
-      <c r="P35" s="243"/>
-      <c r="Q35" s="243"/>
-      <c r="R35" s="243"/>
-      <c r="S35" s="243"/>
-      <c r="T35" s="243"/>
-      <c r="U35" s="243"/>
-      <c r="V35" s="243"/>
-      <c r="W35" s="244"/>
-      <c r="X35" s="225" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y35" s="235"/>
-      <c r="Z35" s="225" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA35" s="235"/>
-      <c r="AB35" s="235"/>
-      <c r="AC35" s="231"/>
+      <c r="D35" s="219"/>
+      <c r="E35" s="219"/>
+      <c r="F35" s="219"/>
+      <c r="G35" s="219"/>
+      <c r="H35" s="219"/>
+      <c r="I35" s="219"/>
+      <c r="J35" s="219"/>
+      <c r="K35" s="219"/>
+      <c r="L35" s="219"/>
+      <c r="M35" s="219"/>
+      <c r="N35" s="219"/>
+      <c r="O35" s="219"/>
+      <c r="P35" s="219"/>
+      <c r="Q35" s="219"/>
+      <c r="R35" s="219"/>
+      <c r="S35" s="219"/>
+      <c r="T35" s="219"/>
+      <c r="U35" s="219"/>
+      <c r="V35" s="219"/>
+      <c r="W35" s="220"/>
+      <c r="X35" s="198" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y35" s="200"/>
+      <c r="Z35" s="198" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA35" s="200"/>
+      <c r="AB35" s="200"/>
+      <c r="AC35" s="189"/>
       <c r="AD35" s="85"/>
       <c r="AE35" s="86"/>
       <c r="AF35" s="87"/>
-      <c r="AG35" s="223"/>
+      <c r="AG35" s="203"/>
       <c r="AH35" s="111" t="s">
         <v>67</v>
       </c>
@@ -4592,39 +4592,39 @@
       </c>
     </row>
     <row r="36" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A36" s="178"/>
+      <c r="A36" s="260"/>
       <c r="B36" s="96"/>
-      <c r="C36" s="245"/>
-      <c r="D36" s="245"/>
-      <c r="E36" s="245"/>
-      <c r="F36" s="245"/>
-      <c r="G36" s="245"/>
-      <c r="H36" s="245"/>
-      <c r="I36" s="245"/>
-      <c r="J36" s="245"/>
-      <c r="K36" s="245"/>
-      <c r="L36" s="245"/>
-      <c r="M36" s="245"/>
-      <c r="N36" s="245"/>
-      <c r="O36" s="245"/>
-      <c r="P36" s="245"/>
-      <c r="Q36" s="245"/>
-      <c r="R36" s="245"/>
-      <c r="S36" s="245"/>
-      <c r="T36" s="245"/>
-      <c r="U36" s="245"/>
-      <c r="V36" s="245"/>
-      <c r="W36" s="246"/>
-      <c r="X36" s="226"/>
-      <c r="Y36" s="236"/>
-      <c r="Z36" s="226"/>
-      <c r="AA36" s="236"/>
-      <c r="AB36" s="236"/>
-      <c r="AC36" s="232"/>
+      <c r="C36" s="221"/>
+      <c r="D36" s="221"/>
+      <c r="E36" s="221"/>
+      <c r="F36" s="221"/>
+      <c r="G36" s="221"/>
+      <c r="H36" s="221"/>
+      <c r="I36" s="221"/>
+      <c r="J36" s="221"/>
+      <c r="K36" s="221"/>
+      <c r="L36" s="221"/>
+      <c r="M36" s="221"/>
+      <c r="N36" s="221"/>
+      <c r="O36" s="221"/>
+      <c r="P36" s="221"/>
+      <c r="Q36" s="221"/>
+      <c r="R36" s="221"/>
+      <c r="S36" s="221"/>
+      <c r="T36" s="221"/>
+      <c r="U36" s="221"/>
+      <c r="V36" s="221"/>
+      <c r="W36" s="222"/>
+      <c r="X36" s="199"/>
+      <c r="Y36" s="201"/>
+      <c r="Z36" s="199"/>
+      <c r="AA36" s="201"/>
+      <c r="AB36" s="201"/>
+      <c r="AC36" s="190"/>
       <c r="AD36" s="85"/>
       <c r="AE36" s="86"/>
       <c r="AF36" s="87"/>
-      <c r="AG36" s="223"/>
+      <c r="AG36" s="203"/>
       <c r="AH36" s="111" t="s">
         <v>68</v>
       </c>
@@ -4666,7 +4666,7 @@
       </c>
     </row>
     <row r="37" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A37" s="178"/>
+      <c r="A37" s="260"/>
       <c r="B37" s="102">
         <v>4</v>
       </c>
@@ -4706,7 +4706,7 @@
       <c r="AD37" s="85"/>
       <c r="AE37" s="86"/>
       <c r="AF37" s="87"/>
-      <c r="AG37" s="223"/>
+      <c r="AG37" s="203"/>
       <c r="AH37" s="111" t="s">
         <v>70</v>
       </c>
@@ -4748,7 +4748,7 @@
       </c>
     </row>
     <row r="38" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A38" s="178"/>
+      <c r="A38" s="260"/>
       <c r="B38" s="120">
         <v>5</v>
       </c>
@@ -4784,7 +4784,7 @@
       <c r="AD38" s="85"/>
       <c r="AE38" s="86"/>
       <c r="AF38" s="87"/>
-      <c r="AG38" s="223"/>
+      <c r="AG38" s="203"/>
       <c r="AH38" s="111" t="s">
         <v>72</v>
       </c>
@@ -4826,33 +4826,33 @@
       </c>
     </row>
     <row r="39" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A39" s="178"/>
-      <c r="B39" s="250" t="s">
+      <c r="A39" s="260"/>
+      <c r="B39" s="210" t="s">
         <v>73</v>
       </c>
-      <c r="C39" s="251" t="s">
+      <c r="C39" s="211" t="s">
         <v>74</v>
       </c>
-      <c r="D39" s="252"/>
-      <c r="E39" s="252"/>
-      <c r="F39" s="252"/>
-      <c r="G39" s="252"/>
-      <c r="H39" s="252"/>
-      <c r="I39" s="252"/>
-      <c r="J39" s="252"/>
-      <c r="K39" s="252"/>
-      <c r="L39" s="252"/>
-      <c r="M39" s="252"/>
-      <c r="N39" s="252"/>
-      <c r="O39" s="252"/>
-      <c r="P39" s="252"/>
-      <c r="Q39" s="252"/>
-      <c r="R39" s="252"/>
-      <c r="S39" s="252"/>
-      <c r="T39" s="252"/>
-      <c r="U39" s="252"/>
-      <c r="V39" s="252"/>
-      <c r="W39" s="253"/>
+      <c r="D39" s="212"/>
+      <c r="E39" s="212"/>
+      <c r="F39" s="212"/>
+      <c r="G39" s="212"/>
+      <c r="H39" s="212"/>
+      <c r="I39" s="212"/>
+      <c r="J39" s="212"/>
+      <c r="K39" s="212"/>
+      <c r="L39" s="212"/>
+      <c r="M39" s="212"/>
+      <c r="N39" s="212"/>
+      <c r="O39" s="212"/>
+      <c r="P39" s="212"/>
+      <c r="Q39" s="212"/>
+      <c r="R39" s="212"/>
+      <c r="S39" s="212"/>
+      <c r="T39" s="212"/>
+      <c r="U39" s="212"/>
+      <c r="V39" s="212"/>
+      <c r="W39" s="213"/>
       <c r="X39" s="114" t="s">
         <v>57</v>
       </c>
@@ -4870,7 +4870,7 @@
       <c r="AD39" s="85"/>
       <c r="AE39" s="86"/>
       <c r="AF39" s="87"/>
-      <c r="AG39" s="223"/>
+      <c r="AG39" s="203"/>
       <c r="AH39" s="111" t="s">
         <v>75</v>
       </c>
@@ -4912,31 +4912,31 @@
       </c>
     </row>
     <row r="40" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A40" s="178"/>
-      <c r="B40" s="250"/>
-      <c r="C40" s="251" t="s">
+      <c r="A40" s="260"/>
+      <c r="B40" s="210"/>
+      <c r="C40" s="211" t="s">
         <v>76</v>
       </c>
-      <c r="D40" s="252"/>
-      <c r="E40" s="252"/>
-      <c r="F40" s="252"/>
-      <c r="G40" s="252"/>
-      <c r="H40" s="252"/>
-      <c r="I40" s="252"/>
-      <c r="J40" s="252"/>
-      <c r="K40" s="252"/>
-      <c r="L40" s="252"/>
-      <c r="M40" s="252"/>
-      <c r="N40" s="252"/>
-      <c r="O40" s="252"/>
-      <c r="P40" s="252"/>
-      <c r="Q40" s="252"/>
-      <c r="R40" s="252"/>
-      <c r="S40" s="252"/>
-      <c r="T40" s="252"/>
-      <c r="U40" s="252"/>
-      <c r="V40" s="252"/>
-      <c r="W40" s="253"/>
+      <c r="D40" s="212"/>
+      <c r="E40" s="212"/>
+      <c r="F40" s="212"/>
+      <c r="G40" s="212"/>
+      <c r="H40" s="212"/>
+      <c r="I40" s="212"/>
+      <c r="J40" s="212"/>
+      <c r="K40" s="212"/>
+      <c r="L40" s="212"/>
+      <c r="M40" s="212"/>
+      <c r="N40" s="212"/>
+      <c r="O40" s="212"/>
+      <c r="P40" s="212"/>
+      <c r="Q40" s="212"/>
+      <c r="R40" s="212"/>
+      <c r="S40" s="212"/>
+      <c r="T40" s="212"/>
+      <c r="U40" s="212"/>
+      <c r="V40" s="212"/>
+      <c r="W40" s="213"/>
       <c r="X40" s="114" t="s">
         <v>57</v>
       </c>
@@ -4954,7 +4954,7 @@
       <c r="AD40" s="85"/>
       <c r="AE40" s="86"/>
       <c r="AF40" s="87"/>
-      <c r="AG40" s="223"/>
+      <c r="AG40" s="203"/>
       <c r="AH40" s="111" t="s">
         <v>77</v>
       </c>
@@ -4996,31 +4996,31 @@
       </c>
     </row>
     <row r="41" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A41" s="178"/>
-      <c r="B41" s="250"/>
-      <c r="C41" s="252" t="s">
+      <c r="A41" s="260"/>
+      <c r="B41" s="210"/>
+      <c r="C41" s="212" t="s">
         <v>78</v>
       </c>
-      <c r="D41" s="252"/>
-      <c r="E41" s="252"/>
-      <c r="F41" s="252"/>
-      <c r="G41" s="252"/>
-      <c r="H41" s="252"/>
-      <c r="I41" s="252"/>
-      <c r="J41" s="252"/>
-      <c r="K41" s="252"/>
-      <c r="L41" s="252"/>
-      <c r="M41" s="252"/>
-      <c r="N41" s="252"/>
-      <c r="O41" s="252"/>
-      <c r="P41" s="252"/>
-      <c r="Q41" s="252"/>
-      <c r="R41" s="252"/>
-      <c r="S41" s="252"/>
-      <c r="T41" s="252"/>
-      <c r="U41" s="252"/>
-      <c r="V41" s="252"/>
-      <c r="W41" s="253"/>
+      <c r="D41" s="212"/>
+      <c r="E41" s="212"/>
+      <c r="F41" s="212"/>
+      <c r="G41" s="212"/>
+      <c r="H41" s="212"/>
+      <c r="I41" s="212"/>
+      <c r="J41" s="212"/>
+      <c r="K41" s="212"/>
+      <c r="L41" s="212"/>
+      <c r="M41" s="212"/>
+      <c r="N41" s="212"/>
+      <c r="O41" s="212"/>
+      <c r="P41" s="212"/>
+      <c r="Q41" s="212"/>
+      <c r="R41" s="212"/>
+      <c r="S41" s="212"/>
+      <c r="T41" s="212"/>
+      <c r="U41" s="212"/>
+      <c r="V41" s="212"/>
+      <c r="W41" s="213"/>
       <c r="X41" s="114" t="s">
         <v>57</v>
       </c>
@@ -5040,7 +5040,7 @@
       <c r="AD41" s="85"/>
       <c r="AE41" s="86"/>
       <c r="AF41" s="87"/>
-      <c r="AG41" s="223"/>
+      <c r="AG41" s="203"/>
       <c r="AH41" s="111" t="s">
         <v>79</v>
       </c>
@@ -5082,31 +5082,31 @@
       </c>
     </row>
     <row r="42" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A42" s="178"/>
-      <c r="B42" s="250"/>
-      <c r="C42" s="251" t="s">
+      <c r="A42" s="260"/>
+      <c r="B42" s="210"/>
+      <c r="C42" s="211" t="s">
         <v>80</v>
       </c>
-      <c r="D42" s="252"/>
-      <c r="E42" s="252"/>
-      <c r="F42" s="252"/>
-      <c r="G42" s="252"/>
-      <c r="H42" s="252"/>
-      <c r="I42" s="252"/>
-      <c r="J42" s="252"/>
-      <c r="K42" s="252"/>
-      <c r="L42" s="252"/>
-      <c r="M42" s="252"/>
-      <c r="N42" s="252"/>
-      <c r="O42" s="252"/>
-      <c r="P42" s="252"/>
-      <c r="Q42" s="252"/>
-      <c r="R42" s="252"/>
-      <c r="S42" s="252"/>
-      <c r="T42" s="252"/>
-      <c r="U42" s="252"/>
-      <c r="V42" s="252"/>
-      <c r="W42" s="253"/>
+      <c r="D42" s="212"/>
+      <c r="E42" s="212"/>
+      <c r="F42" s="212"/>
+      <c r="G42" s="212"/>
+      <c r="H42" s="212"/>
+      <c r="I42" s="212"/>
+      <c r="J42" s="212"/>
+      <c r="K42" s="212"/>
+      <c r="L42" s="212"/>
+      <c r="M42" s="212"/>
+      <c r="N42" s="212"/>
+      <c r="O42" s="212"/>
+      <c r="P42" s="212"/>
+      <c r="Q42" s="212"/>
+      <c r="R42" s="212"/>
+      <c r="S42" s="212"/>
+      <c r="T42" s="212"/>
+      <c r="U42" s="212"/>
+      <c r="V42" s="212"/>
+      <c r="W42" s="213"/>
       <c r="X42" s="121" t="s">
         <v>57</v>
       </c>
@@ -5126,7 +5126,7 @@
       <c r="AD42" s="85"/>
       <c r="AE42" s="86"/>
       <c r="AF42" s="87"/>
-      <c r="AG42" s="223"/>
+      <c r="AG42" s="203"/>
       <c r="AH42" s="111" t="s">
         <v>81</v>
       </c>
@@ -5168,31 +5168,31 @@
       </c>
     </row>
     <row r="43" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A43" s="178"/>
-      <c r="B43" s="250"/>
-      <c r="C43" s="254" t="s">
+      <c r="A43" s="260"/>
+      <c r="B43" s="210"/>
+      <c r="C43" s="214" t="s">
         <v>82</v>
       </c>
-      <c r="D43" s="255"/>
-      <c r="E43" s="255"/>
-      <c r="F43" s="255"/>
-      <c r="G43" s="255"/>
-      <c r="H43" s="255"/>
-      <c r="I43" s="255"/>
-      <c r="J43" s="255"/>
-      <c r="K43" s="255"/>
-      <c r="L43" s="255"/>
-      <c r="M43" s="255"/>
-      <c r="N43" s="255"/>
-      <c r="O43" s="255"/>
-      <c r="P43" s="255"/>
-      <c r="Q43" s="255"/>
-      <c r="R43" s="255"/>
-      <c r="S43" s="255"/>
-      <c r="T43" s="255"/>
-      <c r="U43" s="255"/>
-      <c r="V43" s="255"/>
-      <c r="W43" s="256"/>
+      <c r="D43" s="215"/>
+      <c r="E43" s="215"/>
+      <c r="F43" s="215"/>
+      <c r="G43" s="215"/>
+      <c r="H43" s="215"/>
+      <c r="I43" s="215"/>
+      <c r="J43" s="215"/>
+      <c r="K43" s="215"/>
+      <c r="L43" s="215"/>
+      <c r="M43" s="215"/>
+      <c r="N43" s="215"/>
+      <c r="O43" s="215"/>
+      <c r="P43" s="215"/>
+      <c r="Q43" s="215"/>
+      <c r="R43" s="215"/>
+      <c r="S43" s="215"/>
+      <c r="T43" s="215"/>
+      <c r="U43" s="215"/>
+      <c r="V43" s="215"/>
+      <c r="W43" s="216"/>
       <c r="X43" s="121" t="s">
         <v>57</v>
       </c>
@@ -5212,7 +5212,7 @@
       <c r="AD43" s="85"/>
       <c r="AE43" s="86"/>
       <c r="AF43" s="87"/>
-      <c r="AG43" s="223"/>
+      <c r="AG43" s="203"/>
       <c r="AH43" s="111" t="s">
         <v>83</v>
       </c>
@@ -5233,13 +5233,13 @@
       </c>
       <c r="AV43" s="112"/>
       <c r="AW43" s="112"/>
-      <c r="AX43" s="227">
+      <c r="AX43" s="223">
         <f ca="1">RANDBETWEEN(750,800)</f>
-        <v>777</v>
-      </c>
-      <c r="AY43" s="227"/>
-      <c r="AZ43" s="227"/>
-      <c r="BA43" s="227"/>
+        <v>779</v>
+      </c>
+      <c r="AY43" s="223"/>
+      <c r="AZ43" s="223"/>
+      <c r="BA43" s="223"/>
       <c r="BB43" s="113"/>
       <c r="BC43" s="114" t="s">
         <v>64</v>
@@ -5259,31 +5259,31 @@
       </c>
     </row>
     <row r="44" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A44" s="178"/>
-      <c r="B44" s="250"/>
-      <c r="C44" s="254" t="s">
+      <c r="A44" s="260"/>
+      <c r="B44" s="210"/>
+      <c r="C44" s="214" t="s">
         <v>86</v>
       </c>
-      <c r="D44" s="255"/>
-      <c r="E44" s="255"/>
-      <c r="F44" s="255"/>
-      <c r="G44" s="255"/>
-      <c r="H44" s="255"/>
-      <c r="I44" s="255"/>
-      <c r="J44" s="255"/>
-      <c r="K44" s="255"/>
-      <c r="L44" s="255"/>
-      <c r="M44" s="255"/>
-      <c r="N44" s="255"/>
-      <c r="O44" s="255"/>
-      <c r="P44" s="255"/>
-      <c r="Q44" s="255"/>
-      <c r="R44" s="255"/>
-      <c r="S44" s="255"/>
-      <c r="T44" s="255"/>
-      <c r="U44" s="255"/>
-      <c r="V44" s="255"/>
-      <c r="W44" s="256"/>
+      <c r="D44" s="215"/>
+      <c r="E44" s="215"/>
+      <c r="F44" s="215"/>
+      <c r="G44" s="215"/>
+      <c r="H44" s="215"/>
+      <c r="I44" s="215"/>
+      <c r="J44" s="215"/>
+      <c r="K44" s="215"/>
+      <c r="L44" s="215"/>
+      <c r="M44" s="215"/>
+      <c r="N44" s="215"/>
+      <c r="O44" s="215"/>
+      <c r="P44" s="215"/>
+      <c r="Q44" s="215"/>
+      <c r="R44" s="215"/>
+      <c r="S44" s="215"/>
+      <c r="T44" s="215"/>
+      <c r="U44" s="215"/>
+      <c r="V44" s="215"/>
+      <c r="W44" s="216"/>
       <c r="X44" s="114" t="s">
         <v>57</v>
       </c>
@@ -5303,7 +5303,7 @@
       <c r="AD44" s="85"/>
       <c r="AE44" s="86"/>
       <c r="AF44" s="87"/>
-      <c r="AG44" s="223"/>
+      <c r="AG44" s="203"/>
       <c r="AH44" s="111" t="s">
         <v>87</v>
       </c>
@@ -5324,13 +5324,13 @@
       </c>
       <c r="AV44" s="112"/>
       <c r="AW44" s="112"/>
-      <c r="AX44" s="227">
+      <c r="AX44" s="223">
         <f ca="1">RANDBETWEEN(2050,2110)</f>
-        <v>2084</v>
-      </c>
-      <c r="AY44" s="227"/>
-      <c r="AZ44" s="227"/>
-      <c r="BA44" s="227"/>
+        <v>2095</v>
+      </c>
+      <c r="AY44" s="223"/>
+      <c r="AZ44" s="223"/>
+      <c r="BA44" s="223"/>
       <c r="BB44" s="113"/>
       <c r="BC44" s="114" t="s">
         <v>64</v>
@@ -5350,31 +5350,31 @@
       </c>
     </row>
     <row r="45" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A45" s="178"/>
-      <c r="B45" s="250"/>
-      <c r="C45" s="251" t="s">
+      <c r="A45" s="260"/>
+      <c r="B45" s="210"/>
+      <c r="C45" s="211" t="s">
         <v>88</v>
       </c>
-      <c r="D45" s="252"/>
-      <c r="E45" s="252"/>
-      <c r="F45" s="252"/>
-      <c r="G45" s="252"/>
-      <c r="H45" s="252"/>
-      <c r="I45" s="252"/>
-      <c r="J45" s="252"/>
-      <c r="K45" s="252"/>
-      <c r="L45" s="252"/>
-      <c r="M45" s="252"/>
-      <c r="N45" s="252"/>
-      <c r="O45" s="252"/>
-      <c r="P45" s="252"/>
-      <c r="Q45" s="252"/>
-      <c r="R45" s="252"/>
-      <c r="S45" s="252"/>
-      <c r="T45" s="252"/>
-      <c r="U45" s="252"/>
-      <c r="V45" s="252"/>
-      <c r="W45" s="253"/>
+      <c r="D45" s="212"/>
+      <c r="E45" s="212"/>
+      <c r="F45" s="212"/>
+      <c r="G45" s="212"/>
+      <c r="H45" s="212"/>
+      <c r="I45" s="212"/>
+      <c r="J45" s="212"/>
+      <c r="K45" s="212"/>
+      <c r="L45" s="212"/>
+      <c r="M45" s="212"/>
+      <c r="N45" s="212"/>
+      <c r="O45" s="212"/>
+      <c r="P45" s="212"/>
+      <c r="Q45" s="212"/>
+      <c r="R45" s="212"/>
+      <c r="S45" s="212"/>
+      <c r="T45" s="212"/>
+      <c r="U45" s="212"/>
+      <c r="V45" s="212"/>
+      <c r="W45" s="213"/>
       <c r="X45" s="114" t="s">
         <v>57</v>
       </c>
@@ -5394,7 +5394,7 @@
       <c r="AD45" s="85"/>
       <c r="AE45" s="86"/>
       <c r="AF45" s="87"/>
-      <c r="AG45" s="223"/>
+      <c r="AG45" s="203"/>
       <c r="AH45" s="111" t="s">
         <v>89</v>
       </c>
@@ -5436,31 +5436,31 @@
       <c r="BH45" s="115"/>
     </row>
     <row r="46" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A46" s="178"/>
-      <c r="B46" s="250"/>
-      <c r="C46" s="251" t="s">
+      <c r="A46" s="260"/>
+      <c r="B46" s="210"/>
+      <c r="C46" s="211" t="s">
         <v>90</v>
       </c>
-      <c r="D46" s="252"/>
-      <c r="E46" s="252"/>
-      <c r="F46" s="252"/>
-      <c r="G46" s="252"/>
-      <c r="H46" s="252"/>
-      <c r="I46" s="252"/>
-      <c r="J46" s="252"/>
-      <c r="K46" s="252"/>
-      <c r="L46" s="252"/>
-      <c r="M46" s="252"/>
-      <c r="N46" s="252"/>
-      <c r="O46" s="252"/>
-      <c r="P46" s="252"/>
-      <c r="Q46" s="252"/>
-      <c r="R46" s="252"/>
-      <c r="S46" s="252"/>
-      <c r="T46" s="252"/>
-      <c r="U46" s="252"/>
-      <c r="V46" s="252"/>
-      <c r="W46" s="253"/>
+      <c r="D46" s="212"/>
+      <c r="E46" s="212"/>
+      <c r="F46" s="212"/>
+      <c r="G46" s="212"/>
+      <c r="H46" s="212"/>
+      <c r="I46" s="212"/>
+      <c r="J46" s="212"/>
+      <c r="K46" s="212"/>
+      <c r="L46" s="212"/>
+      <c r="M46" s="212"/>
+      <c r="N46" s="212"/>
+      <c r="O46" s="212"/>
+      <c r="P46" s="212"/>
+      <c r="Q46" s="212"/>
+      <c r="R46" s="212"/>
+      <c r="S46" s="212"/>
+      <c r="T46" s="212"/>
+      <c r="U46" s="212"/>
+      <c r="V46" s="212"/>
+      <c r="W46" s="213"/>
       <c r="X46" s="121" t="s">
         <v>64</v>
       </c>
@@ -5480,7 +5480,7 @@
       <c r="AD46" s="85"/>
       <c r="AE46" s="86"/>
       <c r="AF46" s="87"/>
-      <c r="AG46" s="223"/>
+      <c r="AG46" s="203"/>
       <c r="AH46" s="111" t="s">
         <v>91</v>
       </c>
@@ -5522,31 +5522,31 @@
       <c r="BH46" s="131"/>
     </row>
     <row r="47" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A47" s="178"/>
-      <c r="B47" s="250"/>
-      <c r="C47" s="254" t="s">
+      <c r="A47" s="260"/>
+      <c r="B47" s="210"/>
+      <c r="C47" s="214" t="s">
         <v>92</v>
       </c>
-      <c r="D47" s="255"/>
-      <c r="E47" s="255"/>
-      <c r="F47" s="255"/>
-      <c r="G47" s="255"/>
-      <c r="H47" s="255"/>
-      <c r="I47" s="255"/>
-      <c r="J47" s="255"/>
-      <c r="K47" s="255"/>
-      <c r="L47" s="255"/>
-      <c r="M47" s="255"/>
-      <c r="N47" s="255"/>
-      <c r="O47" s="255"/>
-      <c r="P47" s="255"/>
-      <c r="Q47" s="255"/>
-      <c r="R47" s="255"/>
-      <c r="S47" s="255"/>
-      <c r="T47" s="255"/>
-      <c r="U47" s="255"/>
-      <c r="V47" s="255"/>
-      <c r="W47" s="256"/>
+      <c r="D47" s="215"/>
+      <c r="E47" s="215"/>
+      <c r="F47" s="215"/>
+      <c r="G47" s="215"/>
+      <c r="H47" s="215"/>
+      <c r="I47" s="215"/>
+      <c r="J47" s="215"/>
+      <c r="K47" s="215"/>
+      <c r="L47" s="215"/>
+      <c r="M47" s="215"/>
+      <c r="N47" s="215"/>
+      <c r="O47" s="215"/>
+      <c r="P47" s="215"/>
+      <c r="Q47" s="215"/>
+      <c r="R47" s="215"/>
+      <c r="S47" s="215"/>
+      <c r="T47" s="215"/>
+      <c r="U47" s="215"/>
+      <c r="V47" s="215"/>
+      <c r="W47" s="216"/>
       <c r="X47" s="121" t="s">
         <v>64</v>
       </c>
@@ -5566,7 +5566,7 @@
       <c r="AD47" s="85"/>
       <c r="AE47" s="86"/>
       <c r="AF47" s="87"/>
-      <c r="AG47" s="224"/>
+      <c r="AG47" s="204"/>
       <c r="AH47" s="111" t="s">
         <v>93</v>
       </c>
@@ -5606,8 +5606,8 @@
       <c r="BH47" s="122"/>
     </row>
     <row r="48" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A48" s="178"/>
-      <c r="B48" s="250"/>
+      <c r="A48" s="260"/>
+      <c r="B48" s="210"/>
       <c r="C48" s="136" t="s">
         <v>94</v>
       </c>
@@ -5684,8 +5684,8 @@
       <c r="BH48" s="105"/>
     </row>
     <row r="49" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A49" s="178"/>
-      <c r="B49" s="250"/>
+      <c r="A49" s="260"/>
+      <c r="B49" s="210"/>
       <c r="C49" s="136" t="s">
         <v>96</v>
       </c>
@@ -5728,7 +5728,7 @@
       <c r="AD49" s="85"/>
       <c r="AE49" s="86"/>
       <c r="AF49" s="87"/>
-      <c r="AG49" s="222" t="s">
+      <c r="AG49" s="202" t="s">
         <v>97</v>
       </c>
       <c r="AH49" s="139" t="s">
@@ -5768,31 +5768,31 @@
       <c r="BH49" s="115"/>
     </row>
     <row r="50" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A50" s="178"/>
-      <c r="B50" s="250"/>
-      <c r="C50" s="242" t="s">
+      <c r="A50" s="260"/>
+      <c r="B50" s="210"/>
+      <c r="C50" s="205" t="s">
         <v>99</v>
       </c>
-      <c r="D50" s="242"/>
-      <c r="E50" s="242"/>
-      <c r="F50" s="242"/>
-      <c r="G50" s="242"/>
-      <c r="H50" s="242"/>
-      <c r="I50" s="242"/>
-      <c r="J50" s="242"/>
-      <c r="K50" s="242"/>
-      <c r="L50" s="242"/>
-      <c r="M50" s="242"/>
-      <c r="N50" s="242"/>
-      <c r="O50" s="242"/>
-      <c r="P50" s="242"/>
-      <c r="Q50" s="242"/>
-      <c r="R50" s="242"/>
-      <c r="S50" s="242"/>
-      <c r="T50" s="242"/>
-      <c r="U50" s="242"/>
-      <c r="V50" s="242"/>
-      <c r="W50" s="242"/>
+      <c r="D50" s="205"/>
+      <c r="E50" s="205"/>
+      <c r="F50" s="205"/>
+      <c r="G50" s="205"/>
+      <c r="H50" s="205"/>
+      <c r="I50" s="205"/>
+      <c r="J50" s="205"/>
+      <c r="K50" s="205"/>
+      <c r="L50" s="205"/>
+      <c r="M50" s="205"/>
+      <c r="N50" s="205"/>
+      <c r="O50" s="205"/>
+      <c r="P50" s="205"/>
+      <c r="Q50" s="205"/>
+      <c r="R50" s="205"/>
+      <c r="S50" s="205"/>
+      <c r="T50" s="205"/>
+      <c r="U50" s="205"/>
+      <c r="V50" s="205"/>
+      <c r="W50" s="205"/>
       <c r="X50" s="114" t="s">
         <v>57</v>
       </c>
@@ -5812,7 +5812,7 @@
       <c r="AD50" s="85"/>
       <c r="AE50" s="86"/>
       <c r="AF50" s="87"/>
-      <c r="AG50" s="223"/>
+      <c r="AG50" s="203"/>
       <c r="AH50" s="139" t="s">
         <v>100</v>
       </c>
@@ -5848,43 +5848,43 @@
       <c r="BH50" s="105"/>
     </row>
     <row r="51" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A51" s="178"/>
+      <c r="A51" s="260"/>
       <c r="B51" s="141">
         <v>6</v>
       </c>
-      <c r="C51" s="233" t="s">
+      <c r="C51" s="206" t="s">
         <v>101</v>
       </c>
-      <c r="D51" s="233"/>
-      <c r="E51" s="233"/>
-      <c r="F51" s="233"/>
-      <c r="G51" s="233"/>
-      <c r="H51" s="233"/>
-      <c r="I51" s="233"/>
-      <c r="J51" s="233"/>
-      <c r="K51" s="233"/>
-      <c r="L51" s="233"/>
-      <c r="M51" s="233"/>
-      <c r="N51" s="233"/>
-      <c r="O51" s="233"/>
-      <c r="P51" s="233"/>
-      <c r="Q51" s="233"/>
-      <c r="R51" s="233"/>
-      <c r="S51" s="233"/>
-      <c r="T51" s="233"/>
-      <c r="U51" s="233"/>
-      <c r="V51" s="233"/>
-      <c r="W51" s="233"/>
-      <c r="X51" s="233"/>
-      <c r="Y51" s="233"/>
-      <c r="Z51" s="233"/>
-      <c r="AA51" s="233"/>
-      <c r="AB51" s="233"/>
-      <c r="AC51" s="233"/>
+      <c r="D51" s="206"/>
+      <c r="E51" s="206"/>
+      <c r="F51" s="206"/>
+      <c r="G51" s="206"/>
+      <c r="H51" s="206"/>
+      <c r="I51" s="206"/>
+      <c r="J51" s="206"/>
+      <c r="K51" s="206"/>
+      <c r="L51" s="206"/>
+      <c r="M51" s="206"/>
+      <c r="N51" s="206"/>
+      <c r="O51" s="206"/>
+      <c r="P51" s="206"/>
+      <c r="Q51" s="206"/>
+      <c r="R51" s="206"/>
+      <c r="S51" s="206"/>
+      <c r="T51" s="206"/>
+      <c r="U51" s="206"/>
+      <c r="V51" s="206"/>
+      <c r="W51" s="206"/>
+      <c r="X51" s="206"/>
+      <c r="Y51" s="206"/>
+      <c r="Z51" s="206"/>
+      <c r="AA51" s="206"/>
+      <c r="AB51" s="206"/>
+      <c r="AC51" s="206"/>
       <c r="AD51" s="85"/>
       <c r="AE51" s="86"/>
       <c r="AF51" s="87"/>
-      <c r="AG51" s="223"/>
+      <c r="AG51" s="203"/>
       <c r="AH51" s="139" t="s">
         <v>102</v>
       </c>
@@ -5918,33 +5918,33 @@
       <c r="BH51" s="115"/>
     </row>
     <row r="52" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A52" s="178"/>
-      <c r="B52" s="261" t="s">
+      <c r="A52" s="260"/>
+      <c r="B52" s="207" t="s">
         <v>103</v>
       </c>
-      <c r="C52" s="247" t="s">
+      <c r="C52" s="194" t="s">
         <v>104</v>
       </c>
-      <c r="D52" s="248"/>
-      <c r="E52" s="248"/>
-      <c r="F52" s="248"/>
-      <c r="G52" s="248"/>
-      <c r="H52" s="248"/>
-      <c r="I52" s="248"/>
-      <c r="J52" s="248"/>
-      <c r="K52" s="248"/>
-      <c r="L52" s="248"/>
-      <c r="M52" s="248"/>
-      <c r="N52" s="248"/>
-      <c r="O52" s="248"/>
-      <c r="P52" s="248"/>
-      <c r="Q52" s="248"/>
-      <c r="R52" s="248"/>
-      <c r="S52" s="248"/>
-      <c r="T52" s="248"/>
-      <c r="U52" s="248"/>
-      <c r="V52" s="248"/>
-      <c r="W52" s="249"/>
+      <c r="D52" s="195"/>
+      <c r="E52" s="195"/>
+      <c r="F52" s="195"/>
+      <c r="G52" s="195"/>
+      <c r="H52" s="195"/>
+      <c r="I52" s="195"/>
+      <c r="J52" s="195"/>
+      <c r="K52" s="195"/>
+      <c r="L52" s="195"/>
+      <c r="M52" s="195"/>
+      <c r="N52" s="195"/>
+      <c r="O52" s="195"/>
+      <c r="P52" s="195"/>
+      <c r="Q52" s="195"/>
+      <c r="R52" s="195"/>
+      <c r="S52" s="195"/>
+      <c r="T52" s="195"/>
+      <c r="U52" s="195"/>
+      <c r="V52" s="195"/>
+      <c r="W52" s="196"/>
       <c r="X52" s="114" t="s">
         <v>57</v>
       </c>
@@ -5964,7 +5964,7 @@
       <c r="AD52" s="85"/>
       <c r="AE52" s="86"/>
       <c r="AF52" s="87"/>
-      <c r="AG52" s="223"/>
+      <c r="AG52" s="203"/>
       <c r="AH52" s="139" t="s">
         <v>105</v>
       </c>
@@ -6002,31 +6002,31 @@
       <c r="BH52" s="115"/>
     </row>
     <row r="53" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A53" s="178"/>
-      <c r="B53" s="262"/>
-      <c r="C53" s="242" t="s">
+      <c r="A53" s="260"/>
+      <c r="B53" s="208"/>
+      <c r="C53" s="205" t="s">
         <v>107</v>
       </c>
-      <c r="D53" s="242"/>
-      <c r="E53" s="242"/>
-      <c r="F53" s="242"/>
-      <c r="G53" s="242"/>
-      <c r="H53" s="242"/>
-      <c r="I53" s="242"/>
-      <c r="J53" s="242"/>
-      <c r="K53" s="242"/>
-      <c r="L53" s="242"/>
-      <c r="M53" s="242"/>
-      <c r="N53" s="242"/>
-      <c r="O53" s="242"/>
-      <c r="P53" s="242"/>
-      <c r="Q53" s="242"/>
-      <c r="R53" s="242"/>
-      <c r="S53" s="242"/>
-      <c r="T53" s="242"/>
-      <c r="U53" s="242"/>
-      <c r="V53" s="242"/>
-      <c r="W53" s="242"/>
+      <c r="D53" s="205"/>
+      <c r="E53" s="205"/>
+      <c r="F53" s="205"/>
+      <c r="G53" s="205"/>
+      <c r="H53" s="205"/>
+      <c r="I53" s="205"/>
+      <c r="J53" s="205"/>
+      <c r="K53" s="205"/>
+      <c r="L53" s="205"/>
+      <c r="M53" s="205"/>
+      <c r="N53" s="205"/>
+      <c r="O53" s="205"/>
+      <c r="P53" s="205"/>
+      <c r="Q53" s="205"/>
+      <c r="R53" s="205"/>
+      <c r="S53" s="205"/>
+      <c r="T53" s="205"/>
+      <c r="U53" s="205"/>
+      <c r="V53" s="205"/>
+      <c r="W53" s="205"/>
       <c r="X53" s="114" t="s">
         <v>57</v>
       </c>
@@ -6044,7 +6044,7 @@
       <c r="AD53" s="85"/>
       <c r="AE53" s="86"/>
       <c r="AF53" s="87"/>
-      <c r="AG53" s="223"/>
+      <c r="AG53" s="203"/>
       <c r="AH53" s="139" t="s">
         <v>108</v>
       </c>
@@ -6082,31 +6082,31 @@
       <c r="BH53" s="115"/>
     </row>
     <row r="54" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A54" s="178"/>
-      <c r="B54" s="262"/>
-      <c r="C54" s="242" t="s">
+      <c r="A54" s="260"/>
+      <c r="B54" s="208"/>
+      <c r="C54" s="205" t="s">
         <v>111</v>
       </c>
-      <c r="D54" s="242"/>
-      <c r="E54" s="242"/>
-      <c r="F54" s="242"/>
-      <c r="G54" s="242"/>
-      <c r="H54" s="242"/>
-      <c r="I54" s="242"/>
-      <c r="J54" s="242"/>
-      <c r="K54" s="242"/>
-      <c r="L54" s="242"/>
-      <c r="M54" s="242"/>
-      <c r="N54" s="242"/>
-      <c r="O54" s="242"/>
-      <c r="P54" s="242"/>
-      <c r="Q54" s="242"/>
-      <c r="R54" s="242"/>
-      <c r="S54" s="242"/>
-      <c r="T54" s="242"/>
-      <c r="U54" s="242"/>
-      <c r="V54" s="242"/>
-      <c r="W54" s="242"/>
+      <c r="D54" s="205"/>
+      <c r="E54" s="205"/>
+      <c r="F54" s="205"/>
+      <c r="G54" s="205"/>
+      <c r="H54" s="205"/>
+      <c r="I54" s="205"/>
+      <c r="J54" s="205"/>
+      <c r="K54" s="205"/>
+      <c r="L54" s="205"/>
+      <c r="M54" s="205"/>
+      <c r="N54" s="205"/>
+      <c r="O54" s="205"/>
+      <c r="P54" s="205"/>
+      <c r="Q54" s="205"/>
+      <c r="R54" s="205"/>
+      <c r="S54" s="205"/>
+      <c r="T54" s="205"/>
+      <c r="U54" s="205"/>
+      <c r="V54" s="205"/>
+      <c r="W54" s="205"/>
       <c r="X54" s="121" t="s">
         <v>57</v>
       </c>
@@ -6124,7 +6124,7 @@
       <c r="AD54" s="85"/>
       <c r="AE54" s="86"/>
       <c r="AF54" s="87"/>
-      <c r="AG54" s="223"/>
+      <c r="AG54" s="203"/>
       <c r="AH54" s="139" t="s">
         <v>112</v>
       </c>
@@ -6162,31 +6162,31 @@
       <c r="BH54" s="115"/>
     </row>
     <row r="55" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A55" s="178"/>
-      <c r="B55" s="262"/>
-      <c r="C55" s="242" t="s">
+      <c r="A55" s="260"/>
+      <c r="B55" s="208"/>
+      <c r="C55" s="205" t="s">
         <v>114</v>
       </c>
-      <c r="D55" s="242"/>
-      <c r="E55" s="242"/>
-      <c r="F55" s="242"/>
-      <c r="G55" s="242"/>
-      <c r="H55" s="242"/>
-      <c r="I55" s="242"/>
-      <c r="J55" s="242"/>
-      <c r="K55" s="242"/>
-      <c r="L55" s="242"/>
-      <c r="M55" s="242"/>
-      <c r="N55" s="242"/>
-      <c r="O55" s="242"/>
-      <c r="P55" s="242"/>
-      <c r="Q55" s="242"/>
-      <c r="R55" s="242"/>
-      <c r="S55" s="242"/>
-      <c r="T55" s="242"/>
-      <c r="U55" s="242"/>
-      <c r="V55" s="242"/>
-      <c r="W55" s="242"/>
+      <c r="D55" s="205"/>
+      <c r="E55" s="205"/>
+      <c r="F55" s="205"/>
+      <c r="G55" s="205"/>
+      <c r="H55" s="205"/>
+      <c r="I55" s="205"/>
+      <c r="J55" s="205"/>
+      <c r="K55" s="205"/>
+      <c r="L55" s="205"/>
+      <c r="M55" s="205"/>
+      <c r="N55" s="205"/>
+      <c r="O55" s="205"/>
+      <c r="P55" s="205"/>
+      <c r="Q55" s="205"/>
+      <c r="R55" s="205"/>
+      <c r="S55" s="205"/>
+      <c r="T55" s="205"/>
+      <c r="U55" s="205"/>
+      <c r="V55" s="205"/>
+      <c r="W55" s="205"/>
       <c r="X55" s="121" t="s">
         <v>57</v>
       </c>
@@ -6204,7 +6204,7 @@
       <c r="AD55" s="85"/>
       <c r="AE55" s="86"/>
       <c r="AF55" s="87"/>
-      <c r="AG55" s="223"/>
+      <c r="AG55" s="203"/>
       <c r="AH55" s="139" t="s">
         <v>115</v>
       </c>
@@ -6238,31 +6238,31 @@
       <c r="BH55" s="115"/>
     </row>
     <row r="56" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A56" s="178"/>
-      <c r="B56" s="262"/>
-      <c r="C56" s="242" t="s">
+      <c r="A56" s="260"/>
+      <c r="B56" s="208"/>
+      <c r="C56" s="205" t="s">
         <v>116</v>
       </c>
-      <c r="D56" s="242"/>
-      <c r="E56" s="242"/>
-      <c r="F56" s="242"/>
-      <c r="G56" s="242"/>
-      <c r="H56" s="242"/>
-      <c r="I56" s="242"/>
-      <c r="J56" s="242"/>
-      <c r="K56" s="242"/>
-      <c r="L56" s="242"/>
-      <c r="M56" s="242"/>
-      <c r="N56" s="242"/>
-      <c r="O56" s="242"/>
-      <c r="P56" s="242"/>
-      <c r="Q56" s="242"/>
-      <c r="R56" s="242"/>
-      <c r="S56" s="242"/>
-      <c r="T56" s="242"/>
-      <c r="U56" s="242"/>
-      <c r="V56" s="242"/>
-      <c r="W56" s="242"/>
+      <c r="D56" s="205"/>
+      <c r="E56" s="205"/>
+      <c r="F56" s="205"/>
+      <c r="G56" s="205"/>
+      <c r="H56" s="205"/>
+      <c r="I56" s="205"/>
+      <c r="J56" s="205"/>
+      <c r="K56" s="205"/>
+      <c r="L56" s="205"/>
+      <c r="M56" s="205"/>
+      <c r="N56" s="205"/>
+      <c r="O56" s="205"/>
+      <c r="P56" s="205"/>
+      <c r="Q56" s="205"/>
+      <c r="R56" s="205"/>
+      <c r="S56" s="205"/>
+      <c r="T56" s="205"/>
+      <c r="U56" s="205"/>
+      <c r="V56" s="205"/>
+      <c r="W56" s="205"/>
       <c r="X56" s="124" t="s">
         <v>64</v>
       </c>
@@ -6280,7 +6280,7 @@
       <c r="AD56" s="85"/>
       <c r="AE56" s="86"/>
       <c r="AF56" s="87"/>
-      <c r="AG56" s="223"/>
+      <c r="AG56" s="203"/>
       <c r="AH56" s="139" t="s">
         <v>117</v>
       </c>
@@ -6314,31 +6314,31 @@
       <c r="BH56" s="115"/>
     </row>
     <row r="57" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A57" s="178"/>
-      <c r="B57" s="262"/>
-      <c r="C57" s="247" t="s">
+      <c r="A57" s="260"/>
+      <c r="B57" s="208"/>
+      <c r="C57" s="194" t="s">
         <v>118</v>
       </c>
-      <c r="D57" s="248"/>
-      <c r="E57" s="248"/>
-      <c r="F57" s="248"/>
-      <c r="G57" s="248"/>
-      <c r="H57" s="248"/>
-      <c r="I57" s="248"/>
-      <c r="J57" s="248"/>
-      <c r="K57" s="248"/>
-      <c r="L57" s="248"/>
-      <c r="M57" s="248"/>
-      <c r="N57" s="248"/>
-      <c r="O57" s="248"/>
-      <c r="P57" s="248"/>
-      <c r="Q57" s="248"/>
-      <c r="R57" s="248"/>
-      <c r="S57" s="248"/>
-      <c r="T57" s="248"/>
-      <c r="U57" s="248"/>
-      <c r="V57" s="248"/>
-      <c r="W57" s="249"/>
+      <c r="D57" s="195"/>
+      <c r="E57" s="195"/>
+      <c r="F57" s="195"/>
+      <c r="G57" s="195"/>
+      <c r="H57" s="195"/>
+      <c r="I57" s="195"/>
+      <c r="J57" s="195"/>
+      <c r="K57" s="195"/>
+      <c r="L57" s="195"/>
+      <c r="M57" s="195"/>
+      <c r="N57" s="195"/>
+      <c r="O57" s="195"/>
+      <c r="P57" s="195"/>
+      <c r="Q57" s="195"/>
+      <c r="R57" s="195"/>
+      <c r="S57" s="195"/>
+      <c r="T57" s="195"/>
+      <c r="U57" s="195"/>
+      <c r="V57" s="195"/>
+      <c r="W57" s="196"/>
       <c r="X57" s="121" t="s">
         <v>57</v>
       </c>
@@ -6356,7 +6356,7 @@
       <c r="AD57" s="85"/>
       <c r="AE57" s="86"/>
       <c r="AF57" s="87"/>
-      <c r="AG57" s="223"/>
+      <c r="AG57" s="203"/>
       <c r="AH57" s="139" t="s">
         <v>119</v>
       </c>
@@ -6390,51 +6390,51 @@
       <c r="BH57" s="115"/>
     </row>
     <row r="58" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A58" s="178"/>
-      <c r="B58" s="262"/>
-      <c r="C58" s="247" t="s">
+      <c r="A58" s="260"/>
+      <c r="B58" s="208"/>
+      <c r="C58" s="194" t="s">
         <v>120</v>
       </c>
-      <c r="D58" s="248"/>
-      <c r="E58" s="248"/>
-      <c r="F58" s="248"/>
-      <c r="G58" s="248"/>
-      <c r="H58" s="248"/>
-      <c r="I58" s="248"/>
-      <c r="J58" s="248"/>
-      <c r="K58" s="248"/>
-      <c r="L58" s="248"/>
-      <c r="M58" s="248"/>
-      <c r="N58" s="248"/>
-      <c r="O58" s="248"/>
-      <c r="P58" s="248"/>
-      <c r="Q58" s="248"/>
-      <c r="R58" s="248"/>
-      <c r="S58" s="248"/>
-      <c r="T58" s="248"/>
-      <c r="U58" s="248"/>
-      <c r="V58" s="248"/>
-      <c r="W58" s="249"/>
-      <c r="X58" s="225" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y58" s="235"/>
-      <c r="Z58" s="225" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA58" s="235" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB58" s="225" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC58" s="231" t="s">
+      <c r="D58" s="195"/>
+      <c r="E58" s="195"/>
+      <c r="F58" s="195"/>
+      <c r="G58" s="195"/>
+      <c r="H58" s="195"/>
+      <c r="I58" s="195"/>
+      <c r="J58" s="195"/>
+      <c r="K58" s="195"/>
+      <c r="L58" s="195"/>
+      <c r="M58" s="195"/>
+      <c r="N58" s="195"/>
+      <c r="O58" s="195"/>
+      <c r="P58" s="195"/>
+      <c r="Q58" s="195"/>
+      <c r="R58" s="195"/>
+      <c r="S58" s="195"/>
+      <c r="T58" s="195"/>
+      <c r="U58" s="195"/>
+      <c r="V58" s="195"/>
+      <c r="W58" s="196"/>
+      <c r="X58" s="198" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y58" s="200"/>
+      <c r="Z58" s="198" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA58" s="200" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB58" s="198" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC58" s="189" t="s">
         <v>58</v>
       </c>
       <c r="AD58" s="85"/>
       <c r="AE58" s="86"/>
       <c r="AF58" s="87"/>
-      <c r="AG58" s="224"/>
+      <c r="AG58" s="204"/>
       <c r="AH58" s="139" t="s">
         <v>121</v>
       </c>
@@ -6468,37 +6468,37 @@
       <c r="BH58" s="115"/>
     </row>
     <row r="59" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A59" s="178"/>
-      <c r="B59" s="262"/>
-      <c r="C59" s="239" t="s">
+      <c r="A59" s="260"/>
+      <c r="B59" s="208"/>
+      <c r="C59" s="191" t="s">
         <v>122</v>
       </c>
-      <c r="D59" s="240"/>
-      <c r="E59" s="240"/>
-      <c r="F59" s="240"/>
-      <c r="G59" s="240"/>
-      <c r="H59" s="240"/>
-      <c r="I59" s="240"/>
-      <c r="J59" s="240"/>
-      <c r="K59" s="240"/>
-      <c r="L59" s="240"/>
-      <c r="M59" s="240"/>
-      <c r="N59" s="240"/>
-      <c r="O59" s="240"/>
-      <c r="P59" s="240"/>
-      <c r="Q59" s="240"/>
-      <c r="R59" s="240"/>
-      <c r="S59" s="240"/>
-      <c r="T59" s="240"/>
-      <c r="U59" s="240"/>
-      <c r="V59" s="240"/>
-      <c r="W59" s="241"/>
-      <c r="X59" s="226"/>
-      <c r="Y59" s="236"/>
-      <c r="Z59" s="226"/>
-      <c r="AA59" s="236"/>
-      <c r="AB59" s="226"/>
-      <c r="AC59" s="232"/>
+      <c r="D59" s="192"/>
+      <c r="E59" s="192"/>
+      <c r="F59" s="192"/>
+      <c r="G59" s="192"/>
+      <c r="H59" s="192"/>
+      <c r="I59" s="192"/>
+      <c r="J59" s="192"/>
+      <c r="K59" s="192"/>
+      <c r="L59" s="192"/>
+      <c r="M59" s="192"/>
+      <c r="N59" s="192"/>
+      <c r="O59" s="192"/>
+      <c r="P59" s="192"/>
+      <c r="Q59" s="192"/>
+      <c r="R59" s="192"/>
+      <c r="S59" s="192"/>
+      <c r="T59" s="192"/>
+      <c r="U59" s="192"/>
+      <c r="V59" s="192"/>
+      <c r="W59" s="193"/>
+      <c r="X59" s="199"/>
+      <c r="Y59" s="201"/>
+      <c r="Z59" s="199"/>
+      <c r="AA59" s="201"/>
+      <c r="AB59" s="199"/>
+      <c r="AC59" s="190"/>
       <c r="AD59" s="85"/>
       <c r="AE59" s="86"/>
       <c r="AF59" s="87"/>
@@ -6536,31 +6536,31 @@
       <c r="BH59" s="105"/>
     </row>
     <row r="60" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A60" s="178"/>
-      <c r="B60" s="262"/>
-      <c r="C60" s="247" t="s">
+      <c r="A60" s="260"/>
+      <c r="B60" s="208"/>
+      <c r="C60" s="194" t="s">
         <v>124</v>
       </c>
-      <c r="D60" s="248"/>
-      <c r="E60" s="248"/>
-      <c r="F60" s="248"/>
-      <c r="G60" s="248"/>
-      <c r="H60" s="248"/>
-      <c r="I60" s="248"/>
-      <c r="J60" s="248"/>
-      <c r="K60" s="248"/>
-      <c r="L60" s="248"/>
-      <c r="M60" s="248"/>
-      <c r="N60" s="248"/>
-      <c r="O60" s="248"/>
-      <c r="P60" s="248"/>
-      <c r="Q60" s="248"/>
-      <c r="R60" s="248"/>
-      <c r="S60" s="248"/>
-      <c r="T60" s="248"/>
-      <c r="U60" s="248"/>
-      <c r="V60" s="248"/>
-      <c r="W60" s="249"/>
+      <c r="D60" s="195"/>
+      <c r="E60" s="195"/>
+      <c r="F60" s="195"/>
+      <c r="G60" s="195"/>
+      <c r="H60" s="195"/>
+      <c r="I60" s="195"/>
+      <c r="J60" s="195"/>
+      <c r="K60" s="195"/>
+      <c r="L60" s="195"/>
+      <c r="M60" s="195"/>
+      <c r="N60" s="195"/>
+      <c r="O60" s="195"/>
+      <c r="P60" s="195"/>
+      <c r="Q60" s="195"/>
+      <c r="R60" s="195"/>
+      <c r="S60" s="195"/>
+      <c r="T60" s="195"/>
+      <c r="U60" s="195"/>
+      <c r="V60" s="195"/>
+      <c r="W60" s="196"/>
       <c r="X60" s="114" t="s">
         <v>57</v>
       </c>
@@ -6578,7 +6578,7 @@
       <c r="AD60" s="85"/>
       <c r="AE60" s="86"/>
       <c r="AF60" s="87"/>
-      <c r="AG60" s="260" t="s">
+      <c r="AG60" s="197" t="s">
         <v>125</v>
       </c>
       <c r="AH60" s="139" t="s">
@@ -6616,49 +6616,49 @@
       <c r="BH60" s="115"/>
     </row>
     <row r="61" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A61" s="178"/>
-      <c r="B61" s="262"/>
-      <c r="C61" s="247" t="s">
+      <c r="A61" s="260"/>
+      <c r="B61" s="208"/>
+      <c r="C61" s="194" t="s">
         <v>127</v>
       </c>
-      <c r="D61" s="248"/>
-      <c r="E61" s="248"/>
-      <c r="F61" s="248"/>
-      <c r="G61" s="248"/>
-      <c r="H61" s="248"/>
-      <c r="I61" s="248"/>
-      <c r="J61" s="248"/>
-      <c r="K61" s="248"/>
-      <c r="L61" s="248"/>
-      <c r="M61" s="248"/>
-      <c r="N61" s="248"/>
-      <c r="O61" s="248"/>
-      <c r="P61" s="248"/>
-      <c r="Q61" s="248"/>
-      <c r="R61" s="248"/>
-      <c r="S61" s="248"/>
-      <c r="T61" s="248"/>
-      <c r="U61" s="248"/>
-      <c r="V61" s="248"/>
-      <c r="W61" s="249"/>
-      <c r="X61" s="225" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y61" s="225"/>
-      <c r="Z61" s="225" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA61" s="225"/>
-      <c r="AB61" s="225" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC61" s="237" t="s">
+      <c r="D61" s="195"/>
+      <c r="E61" s="195"/>
+      <c r="F61" s="195"/>
+      <c r="G61" s="195"/>
+      <c r="H61" s="195"/>
+      <c r="I61" s="195"/>
+      <c r="J61" s="195"/>
+      <c r="K61" s="195"/>
+      <c r="L61" s="195"/>
+      <c r="M61" s="195"/>
+      <c r="N61" s="195"/>
+      <c r="O61" s="195"/>
+      <c r="P61" s="195"/>
+      <c r="Q61" s="195"/>
+      <c r="R61" s="195"/>
+      <c r="S61" s="195"/>
+      <c r="T61" s="195"/>
+      <c r="U61" s="195"/>
+      <c r="V61" s="195"/>
+      <c r="W61" s="196"/>
+      <c r="X61" s="198" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y61" s="198"/>
+      <c r="Z61" s="198" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA61" s="198"/>
+      <c r="AB61" s="198" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC61" s="217" t="s">
         <v>58</v>
       </c>
       <c r="AD61" s="144"/>
       <c r="AE61" s="86"/>
       <c r="AF61" s="87"/>
-      <c r="AG61" s="260"/>
+      <c r="AG61" s="197"/>
       <c r="AH61" s="139" t="s">
         <v>128</v>
       </c>
@@ -6694,41 +6694,41 @@
       <c r="BH61" s="115"/>
     </row>
     <row r="62" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A62" s="178"/>
-      <c r="B62" s="262"/>
-      <c r="C62" s="239" t="s">
+      <c r="A62" s="260"/>
+      <c r="B62" s="208"/>
+      <c r="C62" s="191" t="s">
         <v>129</v>
       </c>
-      <c r="D62" s="240"/>
-      <c r="E62" s="240"/>
-      <c r="F62" s="240"/>
-      <c r="G62" s="240"/>
-      <c r="H62" s="240"/>
-      <c r="I62" s="240"/>
-      <c r="J62" s="240"/>
-      <c r="K62" s="240"/>
-      <c r="L62" s="240"/>
-      <c r="M62" s="240"/>
-      <c r="N62" s="240"/>
-      <c r="O62" s="240"/>
-      <c r="P62" s="240"/>
-      <c r="Q62" s="240"/>
-      <c r="R62" s="240"/>
-      <c r="S62" s="240"/>
-      <c r="T62" s="240"/>
-      <c r="U62" s="240"/>
-      <c r="V62" s="240"/>
-      <c r="W62" s="241"/>
-      <c r="X62" s="226"/>
-      <c r="Y62" s="226"/>
-      <c r="Z62" s="226"/>
-      <c r="AA62" s="226"/>
-      <c r="AB62" s="226"/>
-      <c r="AC62" s="238"/>
+      <c r="D62" s="192"/>
+      <c r="E62" s="192"/>
+      <c r="F62" s="192"/>
+      <c r="G62" s="192"/>
+      <c r="H62" s="192"/>
+      <c r="I62" s="192"/>
+      <c r="J62" s="192"/>
+      <c r="K62" s="192"/>
+      <c r="L62" s="192"/>
+      <c r="M62" s="192"/>
+      <c r="N62" s="192"/>
+      <c r="O62" s="192"/>
+      <c r="P62" s="192"/>
+      <c r="Q62" s="192"/>
+      <c r="R62" s="192"/>
+      <c r="S62" s="192"/>
+      <c r="T62" s="192"/>
+      <c r="U62" s="192"/>
+      <c r="V62" s="192"/>
+      <c r="W62" s="193"/>
+      <c r="X62" s="199"/>
+      <c r="Y62" s="199"/>
+      <c r="Z62" s="199"/>
+      <c r="AA62" s="199"/>
+      <c r="AB62" s="199"/>
+      <c r="AC62" s="218"/>
       <c r="AD62" s="145"/>
       <c r="AE62" s="86"/>
       <c r="AF62" s="87"/>
-      <c r="AG62" s="260"/>
+      <c r="AG62" s="197"/>
       <c r="AH62" s="139" t="s">
         <v>130</v>
       </c>
@@ -6764,31 +6764,31 @@
       <c r="BH62" s="115"/>
     </row>
     <row r="63" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A63" s="178"/>
-      <c r="B63" s="262"/>
-      <c r="C63" s="242" t="s">
+      <c r="A63" s="260"/>
+      <c r="B63" s="208"/>
+      <c r="C63" s="205" t="s">
         <v>131</v>
       </c>
-      <c r="D63" s="242"/>
-      <c r="E63" s="242"/>
-      <c r="F63" s="242"/>
-      <c r="G63" s="242"/>
-      <c r="H63" s="242"/>
-      <c r="I63" s="242"/>
-      <c r="J63" s="242"/>
-      <c r="K63" s="242"/>
-      <c r="L63" s="242"/>
-      <c r="M63" s="242"/>
-      <c r="N63" s="242"/>
-      <c r="O63" s="242"/>
-      <c r="P63" s="242"/>
-      <c r="Q63" s="242"/>
-      <c r="R63" s="242"/>
-      <c r="S63" s="242"/>
-      <c r="T63" s="242"/>
-      <c r="U63" s="242"/>
-      <c r="V63" s="242"/>
-      <c r="W63" s="242"/>
+      <c r="D63" s="205"/>
+      <c r="E63" s="205"/>
+      <c r="F63" s="205"/>
+      <c r="G63" s="205"/>
+      <c r="H63" s="205"/>
+      <c r="I63" s="205"/>
+      <c r="J63" s="205"/>
+      <c r="K63" s="205"/>
+      <c r="L63" s="205"/>
+      <c r="M63" s="205"/>
+      <c r="N63" s="205"/>
+      <c r="O63" s="205"/>
+      <c r="P63" s="205"/>
+      <c r="Q63" s="205"/>
+      <c r="R63" s="205"/>
+      <c r="S63" s="205"/>
+      <c r="T63" s="205"/>
+      <c r="U63" s="205"/>
+      <c r="V63" s="205"/>
+      <c r="W63" s="205"/>
       <c r="X63" s="121" t="s">
         <v>57</v>
       </c>
@@ -6804,7 +6804,7 @@
       <c r="AD63" s="33"/>
       <c r="AE63" s="144"/>
       <c r="AF63" s="144"/>
-      <c r="AG63" s="260"/>
+      <c r="AG63" s="197"/>
       <c r="AH63" s="139" t="s">
         <v>121</v>
       </c>
@@ -6840,8 +6840,8 @@
       <c r="BH63" s="115"/>
     </row>
     <row r="64" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A64" s="178"/>
-      <c r="B64" s="263"/>
+      <c r="A64" s="260"/>
+      <c r="B64" s="209"/>
       <c r="C64" s="78" t="s">
         <v>132</v>
       </c>
@@ -6878,7 +6878,7 @@
       <c r="AD64" s="33"/>
       <c r="AE64" s="145"/>
       <c r="AF64" s="145"/>
-      <c r="AG64" s="260"/>
+      <c r="AG64" s="197"/>
       <c r="AH64" s="148" t="s">
         <v>133</v>
       </c>
@@ -6914,13 +6914,13 @@
       <c r="BH64" s="115"/>
     </row>
     <row r="65" spans="1:60" ht="11.25" customHeight="1">
-      <c r="A65" s="178"/>
+      <c r="A65" s="260"/>
       <c r="AD65" s="34"/>
       <c r="AE65" s="33"/>
       <c r="AF65" s="33"/>
     </row>
     <row r="66" spans="1:60" ht="9.9" customHeight="1">
-      <c r="A66" s="178"/>
+      <c r="A66" s="260"/>
       <c r="B66" s="152" t="s">
         <v>134</v>
       </c>
@@ -6984,7 +6984,7 @@
       <c r="BH66" s="153"/>
     </row>
     <row r="67" spans="1:60" ht="9.9" customHeight="1">
-      <c r="A67" s="178"/>
+      <c r="A67" s="260"/>
       <c r="B67" s="154" t="s">
         <v>135</v>
       </c>
@@ -7048,22 +7048,22 @@
       <c r="BH67" s="155"/>
     </row>
     <row r="68" spans="1:60" ht="9.9" customHeight="1">
-      <c r="A68" s="178"/>
-      <c r="B68" s="257" t="s">
+      <c r="A68" s="260"/>
+      <c r="B68" s="178" t="s">
         <v>136</v>
       </c>
-      <c r="C68" s="257"/>
-      <c r="D68" s="257"/>
-      <c r="E68" s="257"/>
-      <c r="F68" s="257"/>
-      <c r="G68" s="257"/>
-      <c r="H68" s="257"/>
-      <c r="I68" s="257"/>
-      <c r="J68" s="257"/>
-      <c r="K68" s="257"/>
-      <c r="L68" s="257"/>
-      <c r="M68" s="257"/>
-      <c r="N68" s="257"/>
+      <c r="C68" s="178"/>
+      <c r="D68" s="178"/>
+      <c r="E68" s="178"/>
+      <c r="F68" s="178"/>
+      <c r="G68" s="178"/>
+      <c r="H68" s="178"/>
+      <c r="I68" s="178"/>
+      <c r="J68" s="178"/>
+      <c r="K68" s="178"/>
+      <c r="L68" s="178"/>
+      <c r="M68" s="178"/>
+      <c r="N68" s="178"/>
       <c r="O68" s="154"/>
       <c r="P68" s="156"/>
       <c r="Q68" s="154"/>
@@ -7084,12 +7084,12 @@
       <c r="AD68" s="159"/>
       <c r="AE68" s="159"/>
       <c r="AF68" s="160"/>
-      <c r="AG68" s="258" t="s">
+      <c r="AG68" s="179" t="s">
         <v>138</v>
       </c>
-      <c r="AH68" s="258"/>
-      <c r="AI68" s="258"/>
-      <c r="AJ68" s="258"/>
+      <c r="AH68" s="179"/>
+      <c r="AI68" s="179"/>
+      <c r="AJ68" s="179"/>
       <c r="AK68" s="161"/>
       <c r="AL68" s="160"/>
       <c r="AM68" s="160"/>
@@ -7099,15 +7099,15 @@
       <c r="AO68" s="162"/>
       <c r="AP68" s="160"/>
       <c r="AQ68" s="160"/>
-      <c r="AR68" s="259"/>
-      <c r="AS68" s="259"/>
-      <c r="AT68" s="259"/>
-      <c r="AU68" s="259"/>
-      <c r="AV68" s="259"/>
-      <c r="AW68" s="259"/>
-      <c r="AX68" s="259"/>
-      <c r="AY68" s="259"/>
-      <c r="AZ68" s="259"/>
+      <c r="AR68" s="188"/>
+      <c r="AS68" s="188"/>
+      <c r="AT68" s="188"/>
+      <c r="AU68" s="188"/>
+      <c r="AV68" s="188"/>
+      <c r="AW68" s="188"/>
+      <c r="AX68" s="188"/>
+      <c r="AY68" s="188"/>
+      <c r="AZ68" s="188"/>
       <c r="BA68" s="160"/>
       <c r="BB68" s="160"/>
       <c r="BC68" s="160"/>
@@ -7118,23 +7118,23 @@
       <c r="BH68" s="160"/>
     </row>
     <row r="69" spans="1:60" ht="9.9" customHeight="1">
-      <c r="A69" s="178"/>
-      <c r="B69" s="257" t="s">
+      <c r="A69" s="260"/>
+      <c r="B69" s="178" t="s">
         <v>139</v>
       </c>
-      <c r="C69" s="257"/>
-      <c r="D69" s="257"/>
-      <c r="E69" s="257"/>
-      <c r="F69" s="257"/>
-      <c r="G69" s="257"/>
-      <c r="H69" s="257"/>
-      <c r="I69" s="257"/>
-      <c r="J69" s="257"/>
-      <c r="K69" s="257"/>
-      <c r="L69" s="257"/>
-      <c r="M69" s="257"/>
-      <c r="N69" s="257"/>
-      <c r="O69" s="257"/>
+      <c r="C69" s="178"/>
+      <c r="D69" s="178"/>
+      <c r="E69" s="178"/>
+      <c r="F69" s="178"/>
+      <c r="G69" s="178"/>
+      <c r="H69" s="178"/>
+      <c r="I69" s="178"/>
+      <c r="J69" s="178"/>
+      <c r="K69" s="178"/>
+      <c r="L69" s="178"/>
+      <c r="M69" s="178"/>
+      <c r="N69" s="178"/>
+      <c r="O69" s="178"/>
       <c r="P69" s="156"/>
       <c r="Q69" s="154"/>
       <c r="R69" s="154"/>
@@ -7154,12 +7154,12 @@
       <c r="AD69" s="164"/>
       <c r="AE69" s="164"/>
       <c r="AF69" s="160"/>
-      <c r="AG69" s="258" t="s">
+      <c r="AG69" s="179" t="s">
         <v>140</v>
       </c>
-      <c r="AH69" s="258"/>
-      <c r="AI69" s="258"/>
-      <c r="AJ69" s="258"/>
+      <c r="AH69" s="179"/>
+      <c r="AI69" s="179"/>
+      <c r="AJ69" s="179"/>
       <c r="AK69" s="161"/>
       <c r="AL69" s="160"/>
       <c r="AM69" s="160"/>
@@ -7169,15 +7169,15 @@
       <c r="AO69" s="162"/>
       <c r="AP69" s="160"/>
       <c r="AQ69" s="160"/>
-      <c r="AR69" s="264"/>
-      <c r="AS69" s="264"/>
-      <c r="AT69" s="264"/>
-      <c r="AU69" s="264"/>
-      <c r="AV69" s="264"/>
-      <c r="AW69" s="264"/>
-      <c r="AX69" s="264"/>
-      <c r="AY69" s="264"/>
-      <c r="AZ69" s="264"/>
+      <c r="AR69" s="180"/>
+      <c r="AS69" s="180"/>
+      <c r="AT69" s="180"/>
+      <c r="AU69" s="180"/>
+      <c r="AV69" s="180"/>
+      <c r="AW69" s="180"/>
+      <c r="AX69" s="180"/>
+      <c r="AY69" s="180"/>
+      <c r="AZ69" s="180"/>
       <c r="BA69" s="160"/>
       <c r="BB69" s="160"/>
       <c r="BC69" s="160"/>
@@ -7188,7 +7188,7 @@
       <c r="BH69" s="160"/>
     </row>
     <row r="70" spans="1:60" ht="9.9" customHeight="1">
-      <c r="A70" s="178"/>
+      <c r="A70" s="260"/>
       <c r="B70" s="154"/>
       <c r="C70" s="154"/>
       <c r="D70" s="154"/>
@@ -7250,7 +7250,7 @@
       <c r="BH70" s="160"/>
     </row>
     <row r="71" spans="1:60" ht="9.9" customHeight="1">
-      <c r="A71" s="178"/>
+      <c r="A71" s="260"/>
       <c r="B71" s="165" t="s">
         <v>141</v>
       </c>
@@ -7314,7 +7314,7 @@
       <c r="BH71" s="166"/>
     </row>
     <row r="72" spans="1:60" ht="9.9" customHeight="1">
-      <c r="A72" s="178"/>
+      <c r="A72" s="260"/>
       <c r="B72" s="165" t="s">
         <v>142</v>
       </c>
@@ -7378,7 +7378,7 @@
       <c r="BH72" s="166"/>
     </row>
     <row r="73" spans="1:60" ht="9.9" customHeight="1">
-      <c r="A73" s="178"/>
+      <c r="A73" s="260"/>
       <c r="B73" s="165" t="s">
         <v>143</v>
       </c>
@@ -7442,18 +7442,18 @@
       <c r="BH73" s="166"/>
     </row>
     <row r="74" spans="1:60" ht="17.25" customHeight="1">
-      <c r="A74" s="178"/>
-      <c r="B74" s="265" t="s">
+      <c r="A74" s="260"/>
+      <c r="B74" s="181" t="s">
         <v>144</v>
       </c>
-      <c r="C74" s="265"/>
-      <c r="D74" s="265"/>
-      <c r="E74" s="265"/>
-      <c r="F74" s="265"/>
-      <c r="G74" s="265"/>
-      <c r="H74" s="265"/>
-      <c r="I74" s="265"/>
-      <c r="J74" s="265"/>
+      <c r="C74" s="181"/>
+      <c r="D74" s="181"/>
+      <c r="E74" s="181"/>
+      <c r="F74" s="181"/>
+      <c r="G74" s="181"/>
+      <c r="H74" s="181"/>
+      <c r="I74" s="181"/>
+      <c r="J74" s="181"/>
       <c r="K74" s="167"/>
       <c r="L74" s="167"/>
       <c r="M74" s="167"/>
@@ -7506,7 +7506,7 @@
       <c r="BH74" s="168"/>
     </row>
     <row r="75" spans="1:60" ht="17.25" customHeight="1">
-      <c r="A75" s="178"/>
+      <c r="A75" s="260"/>
       <c r="B75" s="43"/>
       <c r="C75" s="43"/>
       <c r="D75" s="43"/>
@@ -7568,7 +7568,7 @@
       <c r="BH75" s="172"/>
     </row>
     <row r="76" spans="1:60" ht="17.25" customHeight="1">
-      <c r="A76" s="178"/>
+      <c r="A76" s="260"/>
       <c r="B76" s="173"/>
       <c r="C76" s="173"/>
       <c r="D76" s="173"/>
@@ -7630,18 +7630,18 @@
       <c r="BH76" s="172"/>
     </row>
     <row r="77" spans="1:60" ht="17.25" customHeight="1">
-      <c r="A77" s="178"/>
-      <c r="B77" s="265" t="s">
+      <c r="A77" s="260"/>
+      <c r="B77" s="181" t="s">
         <v>145</v>
       </c>
-      <c r="C77" s="265"/>
-      <c r="D77" s="265"/>
-      <c r="E77" s="265"/>
-      <c r="F77" s="265"/>
-      <c r="G77" s="265"/>
-      <c r="H77" s="265"/>
-      <c r="I77" s="265"/>
-      <c r="J77" s="265"/>
+      <c r="C77" s="181"/>
+      <c r="D77" s="181"/>
+      <c r="E77" s="181"/>
+      <c r="F77" s="181"/>
+      <c r="G77" s="181"/>
+      <c r="H77" s="181"/>
+      <c r="I77" s="181"/>
+      <c r="J77" s="181"/>
       <c r="K77" s="171"/>
       <c r="L77" s="171"/>
       <c r="M77" s="171"/>
@@ -7694,7 +7694,7 @@
       <c r="BH77" s="174"/>
     </row>
     <row r="78" spans="1:60" ht="17.25" customHeight="1">
-      <c r="A78" s="178"/>
+      <c r="A78" s="260"/>
       <c r="B78" s="173"/>
       <c r="C78" s="173"/>
       <c r="D78" s="173"/>
@@ -7756,7 +7756,7 @@
       <c r="BH78" s="174"/>
     </row>
     <row r="79" spans="1:60" ht="17.25" customHeight="1">
-      <c r="A79" s="178"/>
+      <c r="A79" s="260"/>
       <c r="B79" s="175"/>
       <c r="C79" s="175"/>
       <c r="D79" s="175"/>
@@ -7818,135 +7818,135 @@
       <c r="BH79" s="174"/>
     </row>
     <row r="80" spans="1:60" ht="9.9" customHeight="1">
-      <c r="A80" s="178"/>
-      <c r="B80" s="266" t="s">
+      <c r="A80" s="260"/>
+      <c r="B80" s="182" t="s">
         <v>146</v>
       </c>
-      <c r="C80" s="266"/>
-      <c r="D80" s="266"/>
-      <c r="E80" s="266"/>
-      <c r="F80" s="266"/>
-      <c r="G80" s="266"/>
-      <c r="H80" s="266"/>
-      <c r="I80" s="266"/>
-      <c r="J80" s="266"/>
-      <c r="K80" s="266"/>
-      <c r="L80" s="266"/>
-      <c r="M80" s="267"/>
-      <c r="N80" s="267"/>
-      <c r="O80" s="267"/>
-      <c r="P80" s="267"/>
-      <c r="Q80" s="267"/>
-      <c r="R80" s="267"/>
-      <c r="S80" s="267"/>
-      <c r="T80" s="267"/>
-      <c r="U80" s="267"/>
-      <c r="V80" s="267"/>
-      <c r="W80" s="267"/>
-      <c r="X80" s="267"/>
-      <c r="Y80" s="267"/>
-      <c r="Z80" s="267"/>
-      <c r="AA80" s="267"/>
-      <c r="AB80" s="267"/>
-      <c r="AC80" s="267"/>
+      <c r="C80" s="182"/>
+      <c r="D80" s="182"/>
+      <c r="E80" s="182"/>
+      <c r="F80" s="182"/>
+      <c r="G80" s="182"/>
+      <c r="H80" s="182"/>
+      <c r="I80" s="182"/>
+      <c r="J80" s="182"/>
+      <c r="K80" s="182"/>
+      <c r="L80" s="182"/>
+      <c r="M80" s="183"/>
+      <c r="N80" s="183"/>
+      <c r="O80" s="183"/>
+      <c r="P80" s="183"/>
+      <c r="Q80" s="183"/>
+      <c r="R80" s="183"/>
+      <c r="S80" s="183"/>
+      <c r="T80" s="183"/>
+      <c r="U80" s="183"/>
+      <c r="V80" s="183"/>
+      <c r="W80" s="183"/>
+      <c r="X80" s="183"/>
+      <c r="Y80" s="183"/>
+      <c r="Z80" s="183"/>
+      <c r="AA80" s="183"/>
+      <c r="AB80" s="183"/>
+      <c r="AC80" s="183"/>
       <c r="AD80" s="162"/>
       <c r="AE80" s="162"/>
       <c r="AF80" s="162"/>
-      <c r="AG80" s="269" t="s">
+      <c r="AG80" s="185" t="s">
         <v>147</v>
       </c>
-      <c r="AH80" s="269"/>
-      <c r="AI80" s="269"/>
-      <c r="AJ80" s="269"/>
-      <c r="AK80" s="269"/>
-      <c r="AL80" s="269"/>
-      <c r="AM80" s="269"/>
-      <c r="AN80" s="269"/>
-      <c r="AO80" s="269"/>
-      <c r="AP80" s="269"/>
-      <c r="AQ80" s="270"/>
-      <c r="AR80" s="270"/>
-      <c r="AS80" s="270"/>
-      <c r="AT80" s="270"/>
-      <c r="AU80" s="270"/>
-      <c r="AV80" s="270"/>
-      <c r="AW80" s="270"/>
-      <c r="AX80" s="270"/>
-      <c r="AY80" s="270"/>
-      <c r="AZ80" s="270"/>
-      <c r="BA80" s="270"/>
-      <c r="BB80" s="270"/>
-      <c r="BC80" s="270"/>
-      <c r="BD80" s="270"/>
-      <c r="BE80" s="270"/>
-      <c r="BF80" s="270"/>
-      <c r="BG80" s="270"/>
-      <c r="BH80" s="270"/>
+      <c r="AH80" s="185"/>
+      <c r="AI80" s="185"/>
+      <c r="AJ80" s="185"/>
+      <c r="AK80" s="185"/>
+      <c r="AL80" s="185"/>
+      <c r="AM80" s="185"/>
+      <c r="AN80" s="185"/>
+      <c r="AO80" s="185"/>
+      <c r="AP80" s="185"/>
+      <c r="AQ80" s="186"/>
+      <c r="AR80" s="186"/>
+      <c r="AS80" s="186"/>
+      <c r="AT80" s="186"/>
+      <c r="AU80" s="186"/>
+      <c r="AV80" s="186"/>
+      <c r="AW80" s="186"/>
+      <c r="AX80" s="186"/>
+      <c r="AY80" s="186"/>
+      <c r="AZ80" s="186"/>
+      <c r="BA80" s="186"/>
+      <c r="BB80" s="186"/>
+      <c r="BC80" s="186"/>
+      <c r="BD80" s="186"/>
+      <c r="BE80" s="186"/>
+      <c r="BF80" s="186"/>
+      <c r="BG80" s="186"/>
+      <c r="BH80" s="186"/>
     </row>
     <row r="81" spans="1:60" ht="11.25" customHeight="1" thickBot="1">
-      <c r="A81" s="178"/>
-      <c r="B81" s="266"/>
-      <c r="C81" s="266"/>
-      <c r="D81" s="266"/>
-      <c r="E81" s="266"/>
-      <c r="F81" s="266"/>
-      <c r="G81" s="266"/>
-      <c r="H81" s="266"/>
-      <c r="I81" s="266"/>
-      <c r="J81" s="266"/>
-      <c r="K81" s="266"/>
-      <c r="L81" s="266"/>
-      <c r="M81" s="268"/>
-      <c r="N81" s="268"/>
-      <c r="O81" s="268"/>
-      <c r="P81" s="268"/>
-      <c r="Q81" s="268"/>
-      <c r="R81" s="268"/>
-      <c r="S81" s="268"/>
-      <c r="T81" s="268"/>
-      <c r="U81" s="268"/>
-      <c r="V81" s="268"/>
-      <c r="W81" s="268"/>
-      <c r="X81" s="268"/>
-      <c r="Y81" s="268"/>
-      <c r="Z81" s="268"/>
-      <c r="AA81" s="268"/>
-      <c r="AB81" s="268"/>
-      <c r="AC81" s="268"/>
+      <c r="A81" s="260"/>
+      <c r="B81" s="182"/>
+      <c r="C81" s="182"/>
+      <c r="D81" s="182"/>
+      <c r="E81" s="182"/>
+      <c r="F81" s="182"/>
+      <c r="G81" s="182"/>
+      <c r="H81" s="182"/>
+      <c r="I81" s="182"/>
+      <c r="J81" s="182"/>
+      <c r="K81" s="182"/>
+      <c r="L81" s="182"/>
+      <c r="M81" s="184"/>
+      <c r="N81" s="184"/>
+      <c r="O81" s="184"/>
+      <c r="P81" s="184"/>
+      <c r="Q81" s="184"/>
+      <c r="R81" s="184"/>
+      <c r="S81" s="184"/>
+      <c r="T81" s="184"/>
+      <c r="U81" s="184"/>
+      <c r="V81" s="184"/>
+      <c r="W81" s="184"/>
+      <c r="X81" s="184"/>
+      <c r="Y81" s="184"/>
+      <c r="Z81" s="184"/>
+      <c r="AA81" s="184"/>
+      <c r="AB81" s="184"/>
+      <c r="AC81" s="184"/>
       <c r="AD81" s="162"/>
       <c r="AE81" s="162"/>
       <c r="AF81" s="162"/>
-      <c r="AG81" s="269"/>
-      <c r="AH81" s="269"/>
-      <c r="AI81" s="269"/>
-      <c r="AJ81" s="269"/>
-      <c r="AK81" s="269"/>
-      <c r="AL81" s="269"/>
-      <c r="AM81" s="269"/>
-      <c r="AN81" s="269"/>
-      <c r="AO81" s="269"/>
-      <c r="AP81" s="269"/>
-      <c r="AQ81" s="271"/>
-      <c r="AR81" s="271"/>
-      <c r="AS81" s="271"/>
-      <c r="AT81" s="271"/>
-      <c r="AU81" s="271"/>
-      <c r="AV81" s="271"/>
-      <c r="AW81" s="271"/>
-      <c r="AX81" s="271"/>
-      <c r="AY81" s="271"/>
-      <c r="AZ81" s="271"/>
-      <c r="BA81" s="271"/>
-      <c r="BB81" s="271"/>
-      <c r="BC81" s="271"/>
-      <c r="BD81" s="271"/>
-      <c r="BE81" s="271"/>
-      <c r="BF81" s="271"/>
-      <c r="BG81" s="271"/>
-      <c r="BH81" s="271"/>
+      <c r="AG81" s="185"/>
+      <c r="AH81" s="185"/>
+      <c r="AI81" s="185"/>
+      <c r="AJ81" s="185"/>
+      <c r="AK81" s="185"/>
+      <c r="AL81" s="185"/>
+      <c r="AM81" s="185"/>
+      <c r="AN81" s="185"/>
+      <c r="AO81" s="185"/>
+      <c r="AP81" s="185"/>
+      <c r="AQ81" s="187"/>
+      <c r="AR81" s="187"/>
+      <c r="AS81" s="187"/>
+      <c r="AT81" s="187"/>
+      <c r="AU81" s="187"/>
+      <c r="AV81" s="187"/>
+      <c r="AW81" s="187"/>
+      <c r="AX81" s="187"/>
+      <c r="AY81" s="187"/>
+      <c r="AZ81" s="187"/>
+      <c r="BA81" s="187"/>
+      <c r="BB81" s="187"/>
+      <c r="BC81" s="187"/>
+      <c r="BD81" s="187"/>
+      <c r="BE81" s="187"/>
+      <c r="BF81" s="187"/>
+      <c r="BG81" s="187"/>
+      <c r="BH81" s="187"/>
     </row>
     <row r="82" spans="1:60" ht="14.25" customHeight="1">
-      <c r="A82" s="178"/>
+      <c r="A82" s="260"/>
       <c r="B82" s="173"/>
       <c r="C82" s="173"/>
       <c r="D82" s="173"/>
@@ -7977,7 +7977,7 @@
       <c r="AC82" s="173"/>
     </row>
     <row r="83" spans="1:60" ht="14.25" customHeight="1">
-      <c r="A83" s="178"/>
+      <c r="A83" s="260"/>
       <c r="C83" s="176" t="s">
         <v>148</v>
       </c>
@@ -8014,7 +8014,7 @@
       </c>
     </row>
     <row r="84" spans="1:60" ht="14.25" customHeight="1">
-      <c r="A84" s="178"/>
+      <c r="A84" s="260"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
@@ -8044,15 +8044,117 @@
     </row>
   </sheetData>
   <mergeCells count="144">
-    <mergeCell ref="B69:O69"/>
-    <mergeCell ref="AG69:AJ69"/>
-    <mergeCell ref="AR69:AZ69"/>
-    <mergeCell ref="B74:J74"/>
-    <mergeCell ref="B77:J77"/>
-    <mergeCell ref="B80:L81"/>
-    <mergeCell ref="M80:AC81"/>
-    <mergeCell ref="AG80:AP81"/>
-    <mergeCell ref="AQ80:BH81"/>
+    <mergeCell ref="A1:A84"/>
+    <mergeCell ref="AN1:BH1"/>
+    <mergeCell ref="V2:AL5"/>
+    <mergeCell ref="AP3:BE3"/>
+    <mergeCell ref="AP4:BE4"/>
+    <mergeCell ref="AN6:AQ7"/>
+    <mergeCell ref="AR6:AS9"/>
+    <mergeCell ref="AT6:AU9"/>
+    <mergeCell ref="AV6:AW9"/>
+    <mergeCell ref="AX6:AY9"/>
+    <mergeCell ref="BG7:BH15"/>
+    <mergeCell ref="AN8:AQ9"/>
+    <mergeCell ref="B9:H10"/>
+    <mergeCell ref="I9:K10"/>
+    <mergeCell ref="L9:T10"/>
+    <mergeCell ref="V9:AC10"/>
+    <mergeCell ref="AD9:AL10"/>
+    <mergeCell ref="AN10:AQ10"/>
+    <mergeCell ref="AR10:AS10"/>
+    <mergeCell ref="AT10:AU10"/>
+    <mergeCell ref="AZ6:BA9"/>
+    <mergeCell ref="BB6:BC9"/>
+    <mergeCell ref="BD6:BE9"/>
+    <mergeCell ref="B7:H8"/>
+    <mergeCell ref="I7:K8"/>
+    <mergeCell ref="L7:T8"/>
+    <mergeCell ref="V7:AC8"/>
+    <mergeCell ref="AD7:AL8"/>
+    <mergeCell ref="B13:K13"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="R13:AK13"/>
+    <mergeCell ref="AL13:AR13"/>
+    <mergeCell ref="AS13:BE13"/>
+    <mergeCell ref="BD10:BE10"/>
+    <mergeCell ref="BB10:BC10"/>
+    <mergeCell ref="AZ10:BA10"/>
+    <mergeCell ref="AX10:AY10"/>
+    <mergeCell ref="AV10:AW10"/>
+    <mergeCell ref="AS15:BE15"/>
+    <mergeCell ref="B12:K12"/>
+    <mergeCell ref="L12:Q12"/>
+    <mergeCell ref="R12:AK12"/>
+    <mergeCell ref="AL12:AR12"/>
+    <mergeCell ref="AS12:BE12"/>
+    <mergeCell ref="AS16:BE16"/>
+    <mergeCell ref="B17:J17"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="H18:O18"/>
+    <mergeCell ref="P18:W18"/>
+    <mergeCell ref="Y18:AD18"/>
+    <mergeCell ref="AE18:AL18"/>
+    <mergeCell ref="AM18:AT18"/>
+    <mergeCell ref="AV18:BE18"/>
+    <mergeCell ref="AV19:BE19"/>
+    <mergeCell ref="P25:W25"/>
+    <mergeCell ref="X25:AD25"/>
+    <mergeCell ref="AE25:AK25"/>
+    <mergeCell ref="AL25:AS25"/>
+    <mergeCell ref="Z28:AA28"/>
+    <mergeCell ref="AC28:AC30"/>
+    <mergeCell ref="BE28:BF28"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="H19:O19"/>
+    <mergeCell ref="P19:W19"/>
+    <mergeCell ref="Y19:AD19"/>
+    <mergeCell ref="AE19:AL19"/>
+    <mergeCell ref="AM19:AT19"/>
+    <mergeCell ref="AG33:AG47"/>
+    <mergeCell ref="BC33:BC34"/>
+    <mergeCell ref="AX43:BA43"/>
+    <mergeCell ref="AX44:BA44"/>
+    <mergeCell ref="BH28:BH30"/>
+    <mergeCell ref="X29:Y29"/>
+    <mergeCell ref="BC29:BD29"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="Z32:Z33"/>
+    <mergeCell ref="AA32:AA33"/>
+    <mergeCell ref="AB32:AB33"/>
+    <mergeCell ref="AC32:AC33"/>
+    <mergeCell ref="AH32:BH32"/>
+    <mergeCell ref="BH33:BH34"/>
+    <mergeCell ref="BD33:BD34"/>
+    <mergeCell ref="BE33:BE34"/>
+    <mergeCell ref="BF33:BF34"/>
+    <mergeCell ref="BG33:BG34"/>
+    <mergeCell ref="AC61:AC62"/>
+    <mergeCell ref="C62:W62"/>
+    <mergeCell ref="C63:W63"/>
+    <mergeCell ref="C35:W36"/>
+    <mergeCell ref="X35:X36"/>
+    <mergeCell ref="Y35:Y36"/>
+    <mergeCell ref="Z35:Z36"/>
+    <mergeCell ref="AA35:AA36"/>
+    <mergeCell ref="AB35:AB36"/>
+    <mergeCell ref="AC35:AC36"/>
+    <mergeCell ref="C53:W53"/>
+    <mergeCell ref="C54:W54"/>
+    <mergeCell ref="C55:W55"/>
+    <mergeCell ref="C56:W56"/>
+    <mergeCell ref="C57:W57"/>
+    <mergeCell ref="B39:B50"/>
+    <mergeCell ref="C39:W39"/>
+    <mergeCell ref="C40:W40"/>
+    <mergeCell ref="C41:W41"/>
+    <mergeCell ref="C42:W42"/>
+    <mergeCell ref="C43:W43"/>
+    <mergeCell ref="C44:W44"/>
+    <mergeCell ref="C45:W45"/>
+    <mergeCell ref="C46:W46"/>
+    <mergeCell ref="C47:W47"/>
     <mergeCell ref="B68:N68"/>
     <mergeCell ref="AG68:AJ68"/>
     <mergeCell ref="AR68:AZ68"/>
@@ -8077,117 +8179,15 @@
     <mergeCell ref="C51:AC51"/>
     <mergeCell ref="B52:B64"/>
     <mergeCell ref="C52:W52"/>
-    <mergeCell ref="B39:B50"/>
-    <mergeCell ref="C39:W39"/>
-    <mergeCell ref="C40:W40"/>
-    <mergeCell ref="C41:W41"/>
-    <mergeCell ref="C42:W42"/>
-    <mergeCell ref="C43:W43"/>
-    <mergeCell ref="C44:W44"/>
-    <mergeCell ref="C45:W45"/>
-    <mergeCell ref="C46:W46"/>
-    <mergeCell ref="C47:W47"/>
-    <mergeCell ref="AC61:AC62"/>
-    <mergeCell ref="C62:W62"/>
-    <mergeCell ref="C63:W63"/>
-    <mergeCell ref="C35:W36"/>
-    <mergeCell ref="X35:X36"/>
-    <mergeCell ref="Y35:Y36"/>
-    <mergeCell ref="Z35:Z36"/>
-    <mergeCell ref="AA35:AA36"/>
-    <mergeCell ref="AB35:AB36"/>
-    <mergeCell ref="AC35:AC36"/>
-    <mergeCell ref="C53:W53"/>
-    <mergeCell ref="C54:W54"/>
-    <mergeCell ref="C55:W55"/>
-    <mergeCell ref="C56:W56"/>
-    <mergeCell ref="C57:W57"/>
-    <mergeCell ref="AG33:AG47"/>
-    <mergeCell ref="BC33:BC34"/>
-    <mergeCell ref="AX43:BA43"/>
-    <mergeCell ref="AX44:BA44"/>
-    <mergeCell ref="BH28:BH30"/>
-    <mergeCell ref="X29:Y29"/>
-    <mergeCell ref="BC29:BD29"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="Z32:Z33"/>
-    <mergeCell ref="AA32:AA33"/>
-    <mergeCell ref="AB32:AB33"/>
-    <mergeCell ref="AC32:AC33"/>
-    <mergeCell ref="AH32:BH32"/>
-    <mergeCell ref="BH33:BH34"/>
-    <mergeCell ref="BD33:BD34"/>
-    <mergeCell ref="BE33:BE34"/>
-    <mergeCell ref="BF33:BF34"/>
-    <mergeCell ref="BG33:BG34"/>
-    <mergeCell ref="AV19:BE19"/>
-    <mergeCell ref="P25:W25"/>
-    <mergeCell ref="X25:AD25"/>
-    <mergeCell ref="AE25:AK25"/>
-    <mergeCell ref="AL25:AS25"/>
-    <mergeCell ref="Z28:AA28"/>
-    <mergeCell ref="AC28:AC30"/>
-    <mergeCell ref="BE28:BF28"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="H19:O19"/>
-    <mergeCell ref="P19:W19"/>
-    <mergeCell ref="Y19:AD19"/>
-    <mergeCell ref="AE19:AL19"/>
-    <mergeCell ref="AM19:AT19"/>
-    <mergeCell ref="AS15:BE15"/>
-    <mergeCell ref="B12:K12"/>
-    <mergeCell ref="L12:Q12"/>
-    <mergeCell ref="R12:AK12"/>
-    <mergeCell ref="AL12:AR12"/>
-    <mergeCell ref="AS12:BE12"/>
-    <mergeCell ref="AS16:BE16"/>
-    <mergeCell ref="B17:J17"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="H18:O18"/>
-    <mergeCell ref="P18:W18"/>
-    <mergeCell ref="Y18:AD18"/>
-    <mergeCell ref="AE18:AL18"/>
-    <mergeCell ref="AM18:AT18"/>
-    <mergeCell ref="AV18:BE18"/>
-    <mergeCell ref="I7:K8"/>
-    <mergeCell ref="L7:T8"/>
-    <mergeCell ref="V7:AC8"/>
-    <mergeCell ref="AD7:AL8"/>
-    <mergeCell ref="B13:K13"/>
-    <mergeCell ref="L13:Q13"/>
-    <mergeCell ref="R13:AK13"/>
-    <mergeCell ref="AL13:AR13"/>
-    <mergeCell ref="AS13:BE13"/>
-    <mergeCell ref="BD10:BE10"/>
-    <mergeCell ref="BB10:BC10"/>
-    <mergeCell ref="AZ10:BA10"/>
-    <mergeCell ref="AX10:AY10"/>
-    <mergeCell ref="AV10:AW10"/>
-    <mergeCell ref="A1:A84"/>
-    <mergeCell ref="AN1:BH1"/>
-    <mergeCell ref="V2:AL5"/>
-    <mergeCell ref="AP3:BE3"/>
-    <mergeCell ref="AP4:BE4"/>
-    <mergeCell ref="AN6:AQ7"/>
-    <mergeCell ref="AR6:AS9"/>
-    <mergeCell ref="AT6:AU9"/>
-    <mergeCell ref="AV6:AW9"/>
-    <mergeCell ref="AX6:AY9"/>
-    <mergeCell ref="BG7:BH15"/>
-    <mergeCell ref="AN8:AQ9"/>
-    <mergeCell ref="B9:H10"/>
-    <mergeCell ref="I9:K10"/>
-    <mergeCell ref="L9:T10"/>
-    <mergeCell ref="V9:AC10"/>
-    <mergeCell ref="AD9:AL10"/>
-    <mergeCell ref="AN10:AQ10"/>
-    <mergeCell ref="AR10:AS10"/>
-    <mergeCell ref="AT10:AU10"/>
-    <mergeCell ref="AZ6:BA9"/>
-    <mergeCell ref="BB6:BC9"/>
-    <mergeCell ref="BD6:BE9"/>
-    <mergeCell ref="B7:H8"/>
+    <mergeCell ref="B69:O69"/>
+    <mergeCell ref="AG69:AJ69"/>
+    <mergeCell ref="AR69:AZ69"/>
+    <mergeCell ref="B74:J74"/>
+    <mergeCell ref="B77:J77"/>
+    <mergeCell ref="B80:L81"/>
+    <mergeCell ref="M80:AC81"/>
+    <mergeCell ref="AG80:AP81"/>
+    <mergeCell ref="AQ80:BH81"/>
   </mergeCells>
   <pageMargins left="0.78740157480314965" right="0.19685039370078741" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" scale="89" orientation="portrait" r:id="rId1"/>
